--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU20"/>
+  <dimension ref="A1:AU21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1566,27 +1566,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-09-21 15:00:00</t>
+          <t>2026-09-21 14:00:00</t>
         </is>
       </c>
     </row>
@@ -1734,22 +1734,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-09-21 15:30:00</t>
+          <t>2026-09-21 15:00:00</t>
         </is>
       </c>
     </row>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G12">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G14">
@@ -2870,27 +2870,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G16">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-09-21 17:00:00</t>
+          <t>2026-09-21 15:30:00</t>
         </is>
       </c>
     </row>
@@ -3033,27 +3033,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-09-21 19:30:00</t>
+          <t>2026-09-21 17:00:00</t>
         </is>
       </c>
     </row>
@@ -3201,22 +3201,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G18">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G19">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-09-21 21:30:00</t>
+          <t>2026-09-21 19:30:00</t>
         </is>
       </c>
     </row>
@@ -3522,156 +3522,319 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-1</v>
+      </c>
+      <c r="AN20">
+        <v>-1</v>
+      </c>
+      <c r="AO20">
+        <v>-1</v>
+      </c>
+      <c r="AP20">
+        <v>-1</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Dunbeholden</t>
         </is>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-      <c r="AB20">
-        <v>0</v>
-      </c>
-      <c r="AC20">
-        <v>0</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>0</v>
-      </c>
-      <c r="AG20">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>0</v>
-      </c>
-      <c r="AK20">
-        <v>0</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
-        <v>-1</v>
-      </c>
-      <c r="AN20">
-        <v>-1</v>
-      </c>
-      <c r="AO20">
-        <v>-1</v>
-      </c>
-      <c r="AP20">
-        <v>-1</v>
-      </c>
-      <c r="AQ20">
-        <v>0</v>
-      </c>
-      <c r="AR20">
-        <v>0</v>
-      </c>
-      <c r="AS20">
-        <v>0</v>
-      </c>
-      <c r="AT20">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-1</v>
+      </c>
+      <c r="AN21">
+        <v>-1</v>
+      </c>
+      <c r="AO21">
+        <v>-1</v>
+      </c>
+      <c r="AP21">
+        <v>-1</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
         <is>
           <t>2026-09-21 22:00:00</t>
         </is>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU21"/>
+  <dimension ref="A1:AU28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,27 +914,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-09-21 12:00:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-09-21 12:00:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-09-21 12:15:00</t>
+          <t>2026-09-21 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,27 +1403,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-09-21 14:00:00</t>
+          <t>2026-09-21 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,27 +1566,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-09-21 14:00:00</t>
+          <t>2026-09-21 12:15:00</t>
         </is>
       </c>
     </row>
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-09-21 15:00:00</t>
+          <t>2026-09-21 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-09-21 15:00:00</t>
+          <t>2026-09-21 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-09-21 15:30:00</t>
+          <t>2026-09-21 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-09-21 15:30:00</t>
+          <t>2026-09-21 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2381,27 +2381,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-09-21 15:30:00</t>
+          <t>2026-09-21 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-09-21 15:30:00</t>
+          <t>2026-09-21 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,27 +2707,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-09-21 15:30:00</t>
+          <t>2026-09-21 15:00:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-09-21 15:30:00</t>
+          <t>2026-09-21 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3033,27 +3033,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-09-21 17:00:00</t>
+          <t>2026-09-21 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G18">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-09-21 19:30:00</t>
+          <t>2026-09-21 15:30:00</t>
         </is>
       </c>
     </row>
@@ -3359,27 +3359,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G19">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-09-21 19:30:00</t>
+          <t>2026-09-21 15:30:00</t>
         </is>
       </c>
     </row>
@@ -3522,27 +3522,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G20">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-09-21 21:30:00</t>
+          <t>2026-09-21 15:30:00</t>
         </is>
       </c>
     </row>
@@ -3685,156 +3685,1297 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Trento</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pro Vercelli</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-1</v>
+      </c>
+      <c r="AN21">
+        <v>-1</v>
+      </c>
+      <c r="AO21">
+        <v>-1</v>
+      </c>
+      <c r="AP21">
+        <v>-1</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Dolomiti Bellunesi</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lumezzane</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>-1</v>
+      </c>
+      <c r="AN22">
+        <v>-1</v>
+      </c>
+      <c r="AO22">
+        <v>-1</v>
+      </c>
+      <c r="AP22">
+        <v>-1</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Treviso</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Desenzano Calvina</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>-1</v>
+      </c>
+      <c r="AN23">
+        <v>-1</v>
+      </c>
+      <c r="AO23">
+        <v>-1</v>
+      </c>
+      <c r="AP23">
+        <v>-1</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Nueva Chicago</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Patronato</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>-1</v>
+      </c>
+      <c r="AN24">
+        <v>-1</v>
+      </c>
+      <c r="AO24">
+        <v>-1</v>
+      </c>
+      <c r="AP24">
+        <v>-1</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>2026-09-21 17:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Humble Lions</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-1</v>
+      </c>
+      <c r="AN25">
+        <v>-1</v>
+      </c>
+      <c r="AO25">
+        <v>-1</v>
+      </c>
+      <c r="AP25">
+        <v>-1</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2026-09-21 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-1</v>
+      </c>
+      <c r="AN26">
+        <v>-1</v>
+      </c>
+      <c r="AO26">
+        <v>-1</v>
+      </c>
+      <c r="AP26">
+        <v>-1</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>2026-09-21 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-1</v>
+      </c>
+      <c r="AN27">
+        <v>-1</v>
+      </c>
+      <c r="AO27">
+        <v>-1</v>
+      </c>
+      <c r="AP27">
+        <v>-1</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Dunbeholden</t>
         </is>
       </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
-      <c r="AK21">
-        <v>0</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>-1</v>
-      </c>
-      <c r="AN21">
-        <v>-1</v>
-      </c>
-      <c r="AO21">
-        <v>-1</v>
-      </c>
-      <c r="AP21">
-        <v>-1</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21">
-        <v>0</v>
-      </c>
-      <c r="AT21">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>-1</v>
+      </c>
+      <c r="AN28">
+        <v>-1</v>
+      </c>
+      <c r="AO28">
+        <v>-1</v>
+      </c>
+      <c r="AP28">
+        <v>-1</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
         <is>
           <t>2026-09-21 22:00:00</t>
         </is>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU28"/>
+  <dimension ref="A1:AU25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,27 +588,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G2">
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-09-21 10:00:00</t>
+          <t>2026-09-21 11:00:00</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G4">
@@ -1077,27 +1077,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-09-21 11:00:00</t>
+          <t>2026-09-21 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1245,22 +1245,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1403,27 +1403,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-09-21 12:00:00</t>
+          <t>2026-09-21 12:15:00</t>
         </is>
       </c>
     </row>
@@ -1566,27 +1566,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-09-21 12:15:00</t>
+          <t>2026-09-21 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G11">
@@ -2218,27 +2218,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-09-21 13:00:00</t>
+          <t>2026-09-21 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2386,22 +2386,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G13">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-09-21 14:00:00</t>
+          <t>2026-09-21 15:00:00</t>
         </is>
       </c>
     </row>
@@ -2712,22 +2712,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G15">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-09-21 15:00:00</t>
+          <t>2026-09-21 15:30:00</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-09-21 15:00:00</t>
+          <t>2026-09-21 15:30:00</t>
         </is>
       </c>
     </row>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G18">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G19">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G21">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G22">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-09-21 15:30:00</t>
+          <t>2026-09-21 19:30:00</t>
         </is>
       </c>
     </row>
@@ -4011,27 +4011,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-09-21 15:30:00</t>
+          <t>2026-09-21 19:30:00</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G24">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-09-21 17:00:00</t>
+          <t>2026-09-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G25">
@@ -4487,495 +4487,6 @@
         <v>0</v>
       </c>
       <c r="AU25" t="inlineStr">
-        <is>
-          <t>2026-09-21 19:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Operário PR</t>
-        </is>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>0</v>
-      </c>
-      <c r="Y26">
-        <v>0</v>
-      </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-      <c r="AA26">
-        <v>0</v>
-      </c>
-      <c r="AB26">
-        <v>0</v>
-      </c>
-      <c r="AC26">
-        <v>0</v>
-      </c>
-      <c r="AD26">
-        <v>0</v>
-      </c>
-      <c r="AE26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>0</v>
-      </c>
-      <c r="AG26">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>0</v>
-      </c>
-      <c r="AK26">
-        <v>0</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
-        <v>-1</v>
-      </c>
-      <c r="AN26">
-        <v>-1</v>
-      </c>
-      <c r="AO26">
-        <v>-1</v>
-      </c>
-      <c r="AP26">
-        <v>-1</v>
-      </c>
-      <c r="AQ26">
-        <v>0</v>
-      </c>
-      <c r="AR26">
-        <v>0</v>
-      </c>
-      <c r="AS26">
-        <v>0</v>
-      </c>
-      <c r="AT26">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>2026-09-21 19:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Cuiabá</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Náutico</t>
-        </is>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
-        <v>0</v>
-      </c>
-      <c r="AB27">
-        <v>0</v>
-      </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <v>0</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>0</v>
-      </c>
-      <c r="AG27">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>0</v>
-      </c>
-      <c r="AK27">
-        <v>0</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>-1</v>
-      </c>
-      <c r="AN27">
-        <v>-1</v>
-      </c>
-      <c r="AO27">
-        <v>-1</v>
-      </c>
-      <c r="AP27">
-        <v>-1</v>
-      </c>
-      <c r="AQ27">
-        <v>0</v>
-      </c>
-      <c r="AR27">
-        <v>0</v>
-      </c>
-      <c r="AS27">
-        <v>0</v>
-      </c>
-      <c r="AT27">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>2026-09-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Arnett Gardens</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Dunbeholden</t>
-        </is>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>0</v>
-      </c>
-      <c r="AB28">
-        <v>0</v>
-      </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>0</v>
-      </c>
-      <c r="AG28">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>0</v>
-      </c>
-      <c r="AK28">
-        <v>0</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>-1</v>
-      </c>
-      <c r="AN28">
-        <v>-1</v>
-      </c>
-      <c r="AO28">
-        <v>-1</v>
-      </c>
-      <c r="AP28">
-        <v>-1</v>
-      </c>
-      <c r="AQ28">
-        <v>0</v>
-      </c>
-      <c r="AR28">
-        <v>0</v>
-      </c>
-      <c r="AS28">
-        <v>0</v>
-      </c>
-      <c r="AT28">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
         <is>
           <t>2026-09-21 22:00:00</t>
         </is>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU25"/>
+  <dimension ref="A1:AU26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G24">
@@ -4337,156 +4337,319 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-1</v>
+      </c>
+      <c r="AN25">
+        <v>-1</v>
+      </c>
+      <c r="AO25">
+        <v>-1</v>
+      </c>
+      <c r="AP25">
+        <v>-1</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Dunbeholden</t>
         </is>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <v>0</v>
-      </c>
-      <c r="X25">
-        <v>0</v>
-      </c>
-      <c r="Y25">
-        <v>0</v>
-      </c>
-      <c r="Z25">
-        <v>0</v>
-      </c>
-      <c r="AA25">
-        <v>0</v>
-      </c>
-      <c r="AB25">
-        <v>0</v>
-      </c>
-      <c r="AC25">
-        <v>0</v>
-      </c>
-      <c r="AD25">
-        <v>0</v>
-      </c>
-      <c r="AE25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>0</v>
-      </c>
-      <c r="AG25">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>0</v>
-      </c>
-      <c r="AK25">
-        <v>0</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>-1</v>
-      </c>
-      <c r="AN25">
-        <v>-1</v>
-      </c>
-      <c r="AO25">
-        <v>-1</v>
-      </c>
-      <c r="AP25">
-        <v>-1</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-1</v>
+      </c>
+      <c r="AN26">
+        <v>-1</v>
+      </c>
+      <c r="AO26">
+        <v>-1</v>
+      </c>
+      <c r="AP26">
+        <v>-1</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
         <is>
           <t>2026-09-21 22:00:00</t>
         </is>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU26"/>
+  <dimension ref="A1:AU25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1296,55 +1296,55 @@
         <v>2.97</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-09-21 14:00:00</t>
+          <t>2026-09-21 15:00:00</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-09-21 15:00:00</t>
+          <t>2026-09-21 15:30:00</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G17">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G20">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G21">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-09-21 15:30:00</t>
+          <t>2026-09-21 19:30:00</t>
         </is>
       </c>
     </row>
@@ -3853,22 +3853,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G22">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-09-21 19:30:00</t>
+          <t>2026-09-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G24">
@@ -4337,27 +4337,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G25">
@@ -4487,169 +4487,6 @@
         <v>0</v>
       </c>
       <c r="AU25" t="inlineStr">
-        <is>
-          <t>2026-09-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Arnett Gardens</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Dunbeholden</t>
-        </is>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>0</v>
-      </c>
-      <c r="Y26">
-        <v>0</v>
-      </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-      <c r="AA26">
-        <v>0</v>
-      </c>
-      <c r="AB26">
-        <v>0</v>
-      </c>
-      <c r="AC26">
-        <v>0</v>
-      </c>
-      <c r="AD26">
-        <v>0</v>
-      </c>
-      <c r="AE26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>0</v>
-      </c>
-      <c r="AG26">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>0</v>
-      </c>
-      <c r="AK26">
-        <v>0</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
-        <v>-1</v>
-      </c>
-      <c r="AN26">
-        <v>-1</v>
-      </c>
-      <c r="AO26">
-        <v>-1</v>
-      </c>
-      <c r="AP26">
-        <v>-1</v>
-      </c>
-      <c r="AQ26">
-        <v>0</v>
-      </c>
-      <c r="AR26">
-        <v>0</v>
-      </c>
-      <c r="AS26">
-        <v>0</v>
-      </c>
-      <c r="AT26">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
         <is>
           <t>2026-09-21 22:00:00</t>
         </is>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -2437,55 +2437,55 @@
         <v>4.21</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G16">

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL24">
         <v>0</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU25"/>
+  <dimension ref="A1:AU27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2386,22 +2386,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="O13">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="P13">
-        <v>4.21</v>
+        <v>3.75</v>
       </c>
       <c r="Q13">
-        <v>2.25</v>
+        <v>2.81</v>
       </c>
       <c r="R13">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="S13">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="T13">
-        <v>2.91</v>
+        <v>2.13</v>
       </c>
       <c r="U13">
-        <v>2.93</v>
+        <v>3.74</v>
       </c>
       <c r="V13">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="W13">
         <v>1.03</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="Y13">
-        <v>1.31</v>
+        <v>1.68</v>
       </c>
       <c r="Z13">
-        <v>3.32</v>
+        <v>2.15</v>
       </c>
       <c r="AA13">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="AB13">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="AC13">
-        <v>3.28</v>
+        <v>5.9</v>
       </c>
       <c r="AD13">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AE13">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF13">
-        <v>1.85</v>
+        <v>2.42</v>
       </c>
       <c r="AG13">
-        <v>1.81</v>
+        <v>1.49</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AK13">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-09-21 15:30:00</t>
+          <t>2026-09-21 15:00:00</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G16">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G20">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G21">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-09-21 19:30:00</t>
+          <t>2026-09-21 15:30:00</t>
         </is>
       </c>
     </row>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="O22">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="P22">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="Q22">
-        <v>2.4</v>
+        <v>3.07</v>
       </c>
       <c r="R22">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="S22">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="T22">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="U22">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="V22">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W22">
         <v>1.04</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y22">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="Z22">
-        <v>2.66</v>
+        <v>2.37</v>
       </c>
       <c r="AA22">
-        <v>2.25</v>
+        <v>2.76</v>
       </c>
       <c r="AB22">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="AC22">
-        <v>4.1</v>
+        <v>5.45</v>
       </c>
       <c r="AD22">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AE22">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AG22">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AK22">
-        <v>1.96</v>
+        <v>1.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-09-21 19:30:00</t>
+          <t>2026-09-21 19:00:00</t>
         </is>
       </c>
     </row>
@@ -4011,27 +4011,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-09-21 21:30:00</t>
+          <t>2026-09-21 19:05:00</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="O24">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="Q24">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="R24">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="S24">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T24">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U24">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="V24">
         <v>1.29</v>
       </c>
       <c r="W24">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
         <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="Z24">
-        <v>2.83</v>
+        <v>2.66</v>
       </c>
       <c r="AA24">
         <v>2.25</v>
       </c>
       <c r="AB24">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AC24">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
       <c r="AD24">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE24">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF24">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AG24">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-09-21 21:30:00</t>
+          <t>2026-09-21 19:30:00</t>
         </is>
       </c>
     </row>
@@ -4337,156 +4337,482 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CSD Independiente del Valle</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-1</v>
+      </c>
+      <c r="AN25">
+        <v>-1</v>
+      </c>
+      <c r="AO25">
+        <v>-1</v>
+      </c>
+      <c r="AP25">
+        <v>-1</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N26">
+        <v>2.05</v>
+      </c>
+      <c r="O26">
+        <v>3.2</v>
+      </c>
+      <c r="P26">
+        <v>3.15</v>
+      </c>
+      <c r="Q26">
+        <v>2.72</v>
+      </c>
+      <c r="R26">
+        <v>2.09</v>
+      </c>
+      <c r="S26">
+        <v>1.47</v>
+      </c>
+      <c r="T26">
+        <v>2.62</v>
+      </c>
+      <c r="U26">
+        <v>3.18</v>
+      </c>
+      <c r="V26">
+        <v>1.29</v>
+      </c>
+      <c r="W26">
+        <v>1.03</v>
+      </c>
+      <c r="X26">
+        <v>1.03</v>
+      </c>
+      <c r="Y26">
+        <v>1.42</v>
+      </c>
+      <c r="Z26">
+        <v>2.83</v>
+      </c>
+      <c r="AA26">
+        <v>2.25</v>
+      </c>
+      <c r="AB26">
+        <v>1.63</v>
+      </c>
+      <c r="AC26">
+        <v>4.21</v>
+      </c>
+      <c r="AD26">
+        <v>1.22</v>
+      </c>
+      <c r="AE26">
+        <v>1.04</v>
+      </c>
+      <c r="AF26">
+        <v>1.93</v>
+      </c>
+      <c r="AG26">
+        <v>1.8</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>1.23</v>
+      </c>
+      <c r="AK26">
+        <v>1.67</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-1</v>
+      </c>
+      <c r="AN26">
+        <v>-1</v>
+      </c>
+      <c r="AO26">
+        <v>-1</v>
+      </c>
+      <c r="AP26">
+        <v>-1</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Dunbeholden</t>
         </is>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <v>0</v>
-      </c>
-      <c r="X25">
-        <v>0</v>
-      </c>
-      <c r="Y25">
-        <v>0</v>
-      </c>
-      <c r="Z25">
-        <v>0</v>
-      </c>
-      <c r="AA25">
-        <v>0</v>
-      </c>
-      <c r="AB25">
-        <v>0</v>
-      </c>
-      <c r="AC25">
-        <v>0</v>
-      </c>
-      <c r="AD25">
-        <v>0</v>
-      </c>
-      <c r="AE25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>0</v>
-      </c>
-      <c r="AG25">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>0</v>
-      </c>
-      <c r="AK25">
-        <v>0</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>-1</v>
-      </c>
-      <c r="AN25">
-        <v>-1</v>
-      </c>
-      <c r="AO25">
-        <v>-1</v>
-      </c>
-      <c r="AP25">
-        <v>-1</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-1</v>
+      </c>
+      <c r="AN27">
+        <v>-1</v>
+      </c>
+      <c r="AO27">
+        <v>-1</v>
+      </c>
+      <c r="AP27">
+        <v>-1</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
         <is>
           <t>2026-09-21 22:00:00</t>
         </is>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G18">

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="O6">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P6">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="Q6">
         <v>3.08</v>
@@ -1314,22 +1314,22 @@
         <v>1.35</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z6">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AA6">
         <v>2.05</v>
       </c>
       <c r="AB6">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC6">
         <v>3.64</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
         <v>1.47</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,55 +3252,55 @@
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC25">
         <v>0</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU27"/>
+  <dimension ref="A1:AU28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>1.62</v>
+        <v>2.9</v>
       </c>
       <c r="R17">
+        <v>2</v>
+      </c>
+      <c r="S17">
+        <v>1.44</v>
+      </c>
+      <c r="T17">
+        <v>2.63</v>
+      </c>
+      <c r="U17">
+        <v>3.2</v>
+      </c>
+      <c r="V17">
+        <v>1.3</v>
+      </c>
+      <c r="W17">
+        <v>1.05</v>
+      </c>
+      <c r="X17">
+        <v>1.04</v>
+      </c>
+      <c r="Y17">
+        <v>1.38</v>
+      </c>
+      <c r="Z17">
         <v>2.73</v>
       </c>
-      <c r="S17">
-        <v>1.25</v>
-      </c>
-      <c r="T17">
-        <v>3.3</v>
-      </c>
-      <c r="U17">
-        <v>2.25</v>
-      </c>
-      <c r="V17">
-        <v>1.49</v>
-      </c>
-      <c r="W17">
-        <v>1.12</v>
-      </c>
-      <c r="X17">
+      <c r="AA17">
+        <v>2.28</v>
+      </c>
+      <c r="AB17">
+        <v>1.53</v>
+      </c>
+      <c r="AC17">
+        <v>4.25</v>
+      </c>
+      <c r="AD17">
+        <v>1.15</v>
+      </c>
+      <c r="AE17">
         <v>1</v>
       </c>
-      <c r="Y17">
-        <v>1.14</v>
-      </c>
-      <c r="Z17">
-        <v>4.4</v>
-      </c>
-      <c r="AA17">
-        <v>1.66</v>
-      </c>
-      <c r="AB17">
-        <v>2.22</v>
-      </c>
-      <c r="AC17">
-        <v>2.35</v>
-      </c>
-      <c r="AD17">
+      <c r="AF17">
+        <v>1.92</v>
+      </c>
+      <c r="AG17">
+        <v>1.76</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>1.3</v>
+      </c>
+      <c r="AK17">
         <v>1.48</v>
-      </c>
-      <c r="AE17">
-        <v>1.16</v>
-      </c>
-      <c r="AF17">
-        <v>2</v>
-      </c>
-      <c r="AG17">
-        <v>1.67</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.14</v>
-      </c>
-      <c r="AK17">
-        <v>3.75</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="R18">
+        <v>2.73</v>
+      </c>
+      <c r="S18">
+        <v>1.25</v>
+      </c>
+      <c r="T18">
+        <v>3.3</v>
+      </c>
+      <c r="U18">
+        <v>2.25</v>
+      </c>
+      <c r="V18">
+        <v>1.49</v>
+      </c>
+      <c r="W18">
+        <v>1.12</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>1.14</v>
+      </c>
+      <c r="Z18">
+        <v>4.4</v>
+      </c>
+      <c r="AA18">
+        <v>1.66</v>
+      </c>
+      <c r="AB18">
+        <v>2.22</v>
+      </c>
+      <c r="AC18">
+        <v>2.35</v>
+      </c>
+      <c r="AD18">
+        <v>1.48</v>
+      </c>
+      <c r="AE18">
+        <v>1.16</v>
+      </c>
+      <c r="AF18">
         <v>2</v>
       </c>
-      <c r="S18">
-        <v>1.44</v>
-      </c>
-      <c r="T18">
-        <v>2.63</v>
-      </c>
-      <c r="U18">
-        <v>3.2</v>
-      </c>
-      <c r="V18">
-        <v>1.3</v>
-      </c>
-      <c r="W18">
-        <v>1.05</v>
-      </c>
-      <c r="X18">
-        <v>1.04</v>
-      </c>
-      <c r="Y18">
-        <v>1.38</v>
-      </c>
-      <c r="Z18">
-        <v>2.73</v>
-      </c>
-      <c r="AA18">
-        <v>2.28</v>
-      </c>
-      <c r="AB18">
-        <v>1.53</v>
-      </c>
-      <c r="AC18">
-        <v>4.25</v>
-      </c>
-      <c r="AD18">
-        <v>1.15</v>
-      </c>
-      <c r="AE18">
-        <v>1</v>
-      </c>
-      <c r="AF18">
-        <v>1.92</v>
-      </c>
       <c r="AG18">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK18">
-        <v>1.48</v>
+        <v>3.75</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="O22">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="P22">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="Q22">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>2.76</v>
+        <v>2.05</v>
       </c>
       <c r="AB22">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AC22">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-09-21 19:00:00</t>
+          <t>2026-09-21 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4011,27 +4011,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-09-21 19:05:00</t>
+          <t>2026-09-21 19:00:00</t>
         </is>
       </c>
     </row>
@@ -4174,27 +4174,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC24">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK24">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-09-21 19:30:00</t>
+          <t>2026-09-21 19:05:00</t>
         </is>
       </c>
     </row>
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.55</v>
+        <v>1.75</v>
       </c>
       <c r="O25">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA25">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB25">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-09-21 21:30:00</t>
+          <t>2026-09-21 19:30:00</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="O26">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P26">
-        <v>3.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q26">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AB26">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AC26">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK26">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4663,156 +4663,319 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27">
+        <v>2.05</v>
+      </c>
+      <c r="O27">
+        <v>3.2</v>
+      </c>
+      <c r="P27">
+        <v>3.15</v>
+      </c>
+      <c r="Q27">
+        <v>2.72</v>
+      </c>
+      <c r="R27">
+        <v>2.09</v>
+      </c>
+      <c r="S27">
+        <v>1.47</v>
+      </c>
+      <c r="T27">
+        <v>2.62</v>
+      </c>
+      <c r="U27">
+        <v>3.18</v>
+      </c>
+      <c r="V27">
+        <v>1.29</v>
+      </c>
+      <c r="W27">
+        <v>1.03</v>
+      </c>
+      <c r="X27">
+        <v>1.03</v>
+      </c>
+      <c r="Y27">
+        <v>1.42</v>
+      </c>
+      <c r="Z27">
+        <v>2.83</v>
+      </c>
+      <c r="AA27">
+        <v>2.25</v>
+      </c>
+      <c r="AB27">
+        <v>1.63</v>
+      </c>
+      <c r="AC27">
+        <v>4.21</v>
+      </c>
+      <c r="AD27">
+        <v>1.22</v>
+      </c>
+      <c r="AE27">
+        <v>1.04</v>
+      </c>
+      <c r="AF27">
+        <v>1.93</v>
+      </c>
+      <c r="AG27">
+        <v>1.8</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.23</v>
+      </c>
+      <c r="AK27">
+        <v>1.67</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-1</v>
+      </c>
+      <c r="AN27">
+        <v>-1</v>
+      </c>
+      <c r="AO27">
+        <v>-1</v>
+      </c>
+      <c r="AP27">
+        <v>-1</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2026-09-21 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Dunbeholden</t>
         </is>
       </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
-        <v>0</v>
-      </c>
-      <c r="AB27">
-        <v>0</v>
-      </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <v>0</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>0</v>
-      </c>
-      <c r="AG27">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>0</v>
-      </c>
-      <c r="AK27">
-        <v>0</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>-1</v>
-      </c>
-      <c r="AN27">
-        <v>-1</v>
-      </c>
-      <c r="AO27">
-        <v>-1</v>
-      </c>
-      <c r="AP27">
-        <v>-1</v>
-      </c>
-      <c r="AQ27">
-        <v>0</v>
-      </c>
-      <c r="AR27">
-        <v>0</v>
-      </c>
-      <c r="AS27">
-        <v>0</v>
-      </c>
-      <c r="AT27">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>-1</v>
+      </c>
+      <c r="AN28">
+        <v>-1</v>
+      </c>
+      <c r="AO28">
+        <v>-1</v>
+      </c>
+      <c r="AP28">
+        <v>-1</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
         <is>
           <t>2026-09-21 22:00:00</t>
         </is>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -1296,16 +1296,16 @@
         <v>3</v>
       </c>
       <c r="Q6">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="R6">
         <v>1.99</v>
       </c>
       <c r="S6">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T6">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="U6">
         <v>3</v>
@@ -1317,28 +1317,28 @@
         <v>1.02</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z6">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AA6">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB6">
         <v>1.7</v>
       </c>
       <c r="AC6">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="AD6">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE6">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
         <v>1.83</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="O14">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="P14">
-        <v>4.21</v>
+        <v>4.75</v>
       </c>
       <c r="Q14">
         <v>2.25</v>
@@ -2606,10 +2606,10 @@
         <v>2.09</v>
       </c>
       <c r="S14">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T14">
-        <v>2.91</v>
+        <v>2.62</v>
       </c>
       <c r="U14">
         <v>2.93</v>
@@ -2624,10 +2624,10 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z14">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="AA14">
         <v>2</v>
@@ -2636,7 +2636,7 @@
         <v>1.8</v>
       </c>
       <c r="AC14">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AD14">
         <v>1.25</v>
@@ -2648,7 +2648,7 @@
         <v>1.85</v>
       </c>
       <c r="AG14">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2926,19 +2926,19 @@
         <v>2.85</v>
       </c>
       <c r="Q16">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="R16">
         <v>1.91</v>
       </c>
       <c r="S16">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T16">
         <v>2.39</v>
       </c>
       <c r="U16">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V16">
         <v>1.29</v>
@@ -2956,7 +2956,7 @@
         <v>2.56</v>
       </c>
       <c r="AA16">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="AB16">
         <v>1.52</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AK16">
         <v>1.47</v>
@@ -3089,19 +3089,19 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S17">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T17">
-        <v>2.63</v>
+        <v>2.34</v>
       </c>
       <c r="U17">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V17">
         <v>1.3</v>
@@ -3116,7 +3116,7 @@
         <v>1.38</v>
       </c>
       <c r="Z17">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="AA17">
         <v>2.28</v>
@@ -3137,7 +3137,7 @@
         <v>1.92</v>
       </c>
       <c r="AG17">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3249,46 +3249,46 @@
         <v>5.2</v>
       </c>
       <c r="P18">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Q18">
         <v>1.62</v>
       </c>
       <c r="R18">
-        <v>2.73</v>
+        <v>2.43</v>
       </c>
       <c r="S18">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T18">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U18">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V18">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z18">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA18">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AB18">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="AC18">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD18">
         <v>1.48</v>
@@ -3300,7 +3300,7 @@
         <v>2</v>
       </c>
       <c r="AG18">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AK18">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.33</v>
+        <v>2.54</v>
       </c>
       <c r="O22">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P22">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>4.2</v>
       </c>
       <c r="Q25">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R25">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S25">
         <v>1.44</v>
@@ -4405,13 +4405,13 @@
         <v>2.6</v>
       </c>
       <c r="U25">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="V25">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
         <v>1.03</v>
@@ -4423,7 +4423,7 @@
         <v>2.66</v>
       </c>
       <c r="AA25">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB25">
         <v>1.59</v>
@@ -4432,16 +4432,16 @@
         <v>4.1</v>
       </c>
       <c r="AD25">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF25">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AG25">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4553,59 +4553,59 @@
         <v>3.15</v>
       </c>
       <c r="P26">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA26">
+        <v>1.97</v>
+      </c>
+      <c r="AB26">
+        <v>1.78</v>
+      </c>
+      <c r="AC26">
+        <v>3.39</v>
+      </c>
+      <c r="AD26">
+        <v>1.27</v>
+      </c>
+      <c r="AE26">
+        <v>1.05</v>
+      </c>
+      <c r="AF26">
+        <v>1.71</v>
+      </c>
+      <c r="AG26">
         <v>2</v>
       </c>
-      <c r="AB26">
-        <v>1.8</v>
-      </c>
-      <c r="AC26">
-        <v>0</v>
-      </c>
-      <c r="AD26">
-        <v>0</v>
-      </c>
-      <c r="AE26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>0</v>
-      </c>
-      <c r="AG26">
-        <v>0</v>
-      </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,22 +4710,22 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="O27">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P27">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="Q27">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="R27">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="S27">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T27">
         <v>2.62</v>
@@ -4737,13 +4737,13 @@
         <v>1.29</v>
       </c>
       <c r="W27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X27">
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="Z27">
         <v>2.83</v>
@@ -4752,13 +4752,13 @@
         <v>2.25</v>
       </c>
       <c r="AB27">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC27">
-        <v>4.21</v>
+        <v>4.4</v>
       </c>
       <c r="AD27">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE27">
         <v>1.04</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -1317,7 +1317,7 @@
         <v>1.02</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
         <v>1.28</v>
@@ -1335,7 +1335,7 @@
         <v>3.61</v>
       </c>
       <c r="AD6">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE6">
         <v>1.04</v>
@@ -2600,7 +2600,7 @@
         <v>4.75</v>
       </c>
       <c r="Q14">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="R14">
         <v>2.09</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="O16">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P16">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="Q16">
-        <v>3.06</v>
+        <v>2.91</v>
       </c>
       <c r="R16">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S16">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T16">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="U16">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V16">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W16">
         <v>1.01</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z16">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="AA16">
-        <v>2.37</v>
+        <v>2.24</v>
       </c>
       <c r="AB16">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC16">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="AD16">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AE16">
         <v>1.01</v>
       </c>
       <c r="AF16">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK16">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>3.02</v>
+        <v>1.62</v>
       </c>
       <c r="R17">
-        <v>2.01</v>
+        <v>2.42</v>
       </c>
       <c r="S17">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
-        <v>2.34</v>
+        <v>3.12</v>
       </c>
       <c r="U17">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="V17">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="Z17">
-        <v>2.62</v>
+        <v>4.5</v>
       </c>
       <c r="AA17">
-        <v>2.28</v>
+        <v>1.55</v>
       </c>
       <c r="AB17">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="AC17">
-        <v>4.25</v>
+        <v>2.33</v>
       </c>
       <c r="AD17">
-        <v>1.15</v>
+        <v>1.49</v>
       </c>
       <c r="AE17">
+        <v>1.16</v>
+      </c>
+      <c r="AF17">
+        <v>2.04</v>
+      </c>
+      <c r="AG17">
+        <v>1.66</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>1</v>
       </c>
-      <c r="AF17">
-        <v>1.92</v>
-      </c>
-      <c r="AG17">
-        <v>1.73</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.3</v>
-      </c>
       <c r="AK17">
-        <v>1.48</v>
+        <v>3.56</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>1.62</v>
+        <v>3.07</v>
       </c>
       <c r="R18">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="S18">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="T18">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="U18">
-        <v>2.29</v>
+        <v>3.1</v>
       </c>
       <c r="V18">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="W18">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="Z18">
-        <v>4.45</v>
+        <v>2.62</v>
       </c>
       <c r="AA18">
-        <v>1.55</v>
+        <v>2.36</v>
       </c>
       <c r="AB18">
-        <v>2.33</v>
+        <v>1.53</v>
       </c>
       <c r="AC18">
-        <v>2.33</v>
+        <v>4.25</v>
       </c>
       <c r="AD18">
+        <v>1.15</v>
+      </c>
+      <c r="AE18">
+        <v>1</v>
+      </c>
+      <c r="AF18">
+        <v>1.95</v>
+      </c>
+      <c r="AG18">
+        <v>1.76</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.3</v>
+      </c>
+      <c r="AK18">
         <v>1.48</v>
-      </c>
-      <c r="AE18">
-        <v>1.16</v>
-      </c>
-      <c r="AF18">
-        <v>2</v>
-      </c>
-      <c r="AG18">
-        <v>1.65</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1</v>
-      </c>
-      <c r="AK18">
-        <v>3.56</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="O22">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P22">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="O25">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -4405,43 +4405,43 @@
         <v>2.6</v>
       </c>
       <c r="U25">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="V25">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
         <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z25">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AA25">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB25">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC25">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD25">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE25">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF25">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AG25">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O26">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P26">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q26">
         <v>3.48</v>
@@ -4562,40 +4562,40 @@
         <v>1.94</v>
       </c>
       <c r="S26">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="U26">
-        <v>2.73</v>
+        <v>2.97</v>
       </c>
       <c r="V26">
         <v>1.36</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z26">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="AA26">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AB26">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC26">
-        <v>3.39</v>
+        <v>3.28</v>
       </c>
       <c r="AD26">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE26">
         <v>1.05</v>
@@ -4604,7 +4604,7 @@
         <v>1.71</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>3.65</v>
       </c>
       <c r="Q27">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="R27">
         <v>1.88</v>
@@ -4728,19 +4728,19 @@
         <v>1.46</v>
       </c>
       <c r="T27">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U27">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="V27">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
         <v>1.35</v>
@@ -4749,7 +4749,7 @@
         <v>2.83</v>
       </c>
       <c r="AA27">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB27">
         <v>1.61</v>
@@ -4758,16 +4758,16 @@
         <v>4.4</v>
       </c>
       <c r="AD27">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE27">
         <v>1.04</v>
       </c>
       <c r="AF27">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG27">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
         <v>1.74</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -4411,7 +4411,7 @@
         <v>1.29</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
         <v>1.03</v>
@@ -4420,7 +4420,7 @@
         <v>1.36</v>
       </c>
       <c r="Z25">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AA25">
         <v>2.25</v>
@@ -4457,7 +4457,7 @@
         <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>3.65</v>
       </c>
       <c r="Q27">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R27">
         <v>1.88</v>
@@ -4728,28 +4728,28 @@
         <v>1.46</v>
       </c>
       <c r="T27">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="U27">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V27">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W27">
         <v>1.03</v>
       </c>
       <c r="X27">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z27">
         <v>2.83</v>
       </c>
       <c r="AA27">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB27">
         <v>1.61</v>
@@ -4758,16 +4758,16 @@
         <v>4.4</v>
       </c>
       <c r="AD27">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE27">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF27">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG27">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
         <v>1.74</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -1317,7 +1317,7 @@
         <v>1.02</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y6">
         <v>1.28</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="O9">
         <v>3.2</v>
       </c>
       <c r="P9">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -2600,34 +2600,34 @@
         <v>4.75</v>
       </c>
       <c r="Q14">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="R14">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="S14">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U14">
-        <v>2.93</v>
+        <v>3.04</v>
       </c>
       <c r="V14">
         <v>1.36</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z14">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA14">
         <v>2</v>
@@ -2642,13 +2642,13 @@
         <v>1.25</v>
       </c>
       <c r="AE14">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF14">
         <v>1.85</v>
       </c>
       <c r="AG14">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.08</v>
       </c>
       <c r="AK14">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="O16">
         <v>3.05</v>
@@ -2926,7 +2926,7 @@
         <v>2.95</v>
       </c>
       <c r="Q16">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="R16">
         <v>2</v>
@@ -2953,13 +2953,13 @@
         <v>1.38</v>
       </c>
       <c r="Z16">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="AA16">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="AB16">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AC16">
         <v>4.15</v>
@@ -2974,7 +2974,7 @@
         <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK16">
         <v>1.57</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="O17">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="P17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>1.62</v>
       </c>
       <c r="R17">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="S17">
         <v>1.25</v>
@@ -3107,37 +3107,37 @@
         <v>1.57</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z17">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA17">
         <v>1.55</v>
       </c>
       <c r="AB17">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AC17">
         <v>2.33</v>
       </c>
       <c r="AD17">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE17">
         <v>1.16</v>
       </c>
       <c r="AF17">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AG17">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AK17">
         <v>3.56</v>
@@ -3255,19 +3255,19 @@
         <v>3.07</v>
       </c>
       <c r="R18">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S18">
         <v>1.44</v>
       </c>
       <c r="T18">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U18">
         <v>3.1</v>
       </c>
       <c r="V18">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W18">
         <v>1.05</v>
@@ -3282,13 +3282,13 @@
         <v>2.62</v>
       </c>
       <c r="AA18">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="AB18">
         <v>1.53</v>
       </c>
       <c r="AC18">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AD18">
         <v>1.15</v>
@@ -3300,7 +3300,7 @@
         <v>1.95</v>
       </c>
       <c r="AG18">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK18">
         <v>1.48</v>
@@ -3409,28 +3409,28 @@
         <v>1.83</v>
       </c>
       <c r="O19">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P19">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q19">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="R19">
         <v>2</v>
       </c>
       <c r="S19">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T19">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U19">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V19">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W19">
         <v>1.02</v>
@@ -3460,10 +3460,10 @@
         <v>1.01</v>
       </c>
       <c r="AF19">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG19">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P20">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q20">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="R20">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="S20">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T20">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="U20">
-        <v>2.97</v>
+        <v>2.5</v>
       </c>
       <c r="V20">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
+        <v>1.25</v>
+      </c>
+      <c r="Z20">
+        <v>3.28</v>
+      </c>
+      <c r="AA20">
+        <v>2</v>
+      </c>
+      <c r="AB20">
+        <v>1.8</v>
+      </c>
+      <c r="AC20">
+        <v>3.08</v>
+      </c>
+      <c r="AD20">
+        <v>1.28</v>
+      </c>
+      <c r="AE20">
+        <v>1.07</v>
+      </c>
+      <c r="AF20">
+        <v>1.76</v>
+      </c>
+      <c r="AG20">
+        <v>1.88</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
         <v>1.3</v>
       </c>
-      <c r="Z20">
-        <v>2.97</v>
-      </c>
-      <c r="AA20">
-        <v>2.08</v>
-      </c>
-      <c r="AB20">
-        <v>1.73</v>
-      </c>
-      <c r="AC20">
-        <v>3.42</v>
-      </c>
-      <c r="AD20">
-        <v>1.23</v>
-      </c>
-      <c r="AE20">
-        <v>1.04</v>
-      </c>
-      <c r="AF20">
-        <v>1.85</v>
-      </c>
-      <c r="AG20">
-        <v>1.8</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.22</v>
-      </c>
       <c r="AK20">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3738,10 +3738,10 @@
         <v>3</v>
       </c>
       <c r="P21">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q21">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="R21">
         <v>2.05</v>
@@ -3750,25 +3750,25 @@
         <v>1.47</v>
       </c>
       <c r="T21">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="U21">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="V21">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W21">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
         <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z21">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="AA21">
         <v>2.27</v>
@@ -3777,16 +3777,16 @@
         <v>1.61</v>
       </c>
       <c r="AC21">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="AD21">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE21">
         <v>1.02</v>
       </c>
       <c r="AF21">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG21">
         <v>1.83</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK21">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="O22">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="P22">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4556,13 +4556,13 @@
         <v>2.37</v>
       </c>
       <c r="Q26">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="R26">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T26">
         <v>2.8</v>
@@ -4604,7 +4604,7 @@
         <v>1.71</v>
       </c>
       <c r="AG26">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK26">
         <v>1.4</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="O20">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P20">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q20">
+        <v>2.92</v>
+      </c>
+      <c r="R20">
+        <v>2.05</v>
+      </c>
+      <c r="S20">
+        <v>1.47</v>
+      </c>
+      <c r="T20">
         <v>2.38</v>
       </c>
-      <c r="R20">
-        <v>2.24</v>
-      </c>
-      <c r="S20">
-        <v>1.38</v>
-      </c>
-      <c r="T20">
-        <v>2.64</v>
-      </c>
       <c r="U20">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Z20">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="AA20">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="AB20">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AC20">
-        <v>3.08</v>
+        <v>3.92</v>
       </c>
       <c r="AD20">
+        <v>1.18</v>
+      </c>
+      <c r="AE20">
+        <v>1.02</v>
+      </c>
+      <c r="AF20">
+        <v>1.86</v>
+      </c>
+      <c r="AG20">
+        <v>1.83</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
         <v>1.28</v>
       </c>
-      <c r="AE20">
-        <v>1.07</v>
-      </c>
-      <c r="AF20">
-        <v>1.76</v>
-      </c>
-      <c r="AG20">
-        <v>1.88</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.3</v>
-      </c>
       <c r="AK20">
-        <v>1.82</v>
+        <v>1.49</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="O21">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P21">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q21">
-        <v>2.92</v>
+        <v>2.38</v>
       </c>
       <c r="R21">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="S21">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="T21">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="U21">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="V21">
+        <v>1.44</v>
+      </c>
+      <c r="W21">
+        <v>1.08</v>
+      </c>
+      <c r="X21">
+        <v>1.01</v>
+      </c>
+      <c r="Y21">
+        <v>1.25</v>
+      </c>
+      <c r="Z21">
+        <v>3.28</v>
+      </c>
+      <c r="AA21">
+        <v>2</v>
+      </c>
+      <c r="AB21">
+        <v>1.8</v>
+      </c>
+      <c r="AC21">
+        <v>3.08</v>
+      </c>
+      <c r="AD21">
         <v>1.28</v>
       </c>
-      <c r="W21">
-        <v>1.05</v>
-      </c>
-      <c r="X21">
-        <v>1.04</v>
-      </c>
-      <c r="Y21">
-        <v>1.36</v>
-      </c>
-      <c r="Z21">
-        <v>2.7</v>
-      </c>
-      <c r="AA21">
-        <v>2.27</v>
-      </c>
-      <c r="AB21">
-        <v>1.61</v>
-      </c>
-      <c r="AC21">
-        <v>3.92</v>
-      </c>
-      <c r="AD21">
-        <v>1.18</v>
-      </c>
       <c r="AE21">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF21">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="AG21">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.49</v>
+        <v>1.82</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.57</v>
+        <v>2.44</v>
       </c>
       <c r="O22">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="P22">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB22">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC22">
         <v>0</v>
@@ -4411,7 +4411,7 @@
         <v>1.29</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
         <v>1.03</v>
@@ -4438,10 +4438,10 @@
         <v>1.02</v>
       </c>
       <c r="AF25">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG25">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O26">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P26">
-        <v>2.37</v>
+        <v>2.46</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -4574,7 +4574,7 @@
         <v>1.36</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4586,10 +4586,10 @@
         <v>3.14</v>
       </c>
       <c r="AA26">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AB26">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC26">
         <v>3.28</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AK26">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK27">
         <v>1.74</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -1317,7 +1317,7 @@
         <v>1.02</v>
       </c>
       <c r="X6">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>1.28</v>
@@ -2600,7 +2600,7 @@
         <v>4.75</v>
       </c>
       <c r="Q14">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="R14">
         <v>2.05</v>
@@ -2624,10 +2624,10 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z14">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA14">
         <v>2</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="O16">
         <v>3.05</v>
@@ -2929,7 +2929,7 @@
         <v>2.75</v>
       </c>
       <c r="R16">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="S16">
         <v>1.47</v>
@@ -2938,7 +2938,7 @@
         <v>2.38</v>
       </c>
       <c r="U16">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="V16">
         <v>1.26</v>
@@ -2953,13 +2953,13 @@
         <v>1.38</v>
       </c>
       <c r="Z16">
-        <v>2.62</v>
+        <v>2.91</v>
       </c>
       <c r="AA16">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AB16">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC16">
         <v>4.15</v>
@@ -2974,7 +2974,7 @@
         <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK16">
         <v>1.57</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="O17">
         <v>5.25</v>
       </c>
       <c r="P17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q17">
         <v>1.62</v>
@@ -3098,7 +3098,7 @@
         <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="U17">
         <v>2.25</v>
@@ -3113,10 +3113,10 @@
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z17">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="AA17">
         <v>1.55</v>
@@ -3125,10 +3125,10 @@
         <v>2.33</v>
       </c>
       <c r="AC17">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AD17">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE17">
         <v>1.16</v>
@@ -3153,7 +3153,7 @@
         <v>1.03</v>
       </c>
       <c r="AK17">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3255,10 +3255,10 @@
         <v>3.07</v>
       </c>
       <c r="R18">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="S18">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T18">
         <v>2.5</v>
@@ -3267,7 +3267,7 @@
         <v>3.1</v>
       </c>
       <c r="V18">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W18">
         <v>1.05</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK18">
         <v>1.48</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="O3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P3">
         <v>5.2</v>
@@ -2600,7 +2600,7 @@
         <v>4.75</v>
       </c>
       <c r="Q14">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="R14">
         <v>2.05</v>
@@ -2612,7 +2612,7 @@
         <v>2.59</v>
       </c>
       <c r="U14">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="V14">
         <v>1.36</v>
@@ -2624,10 +2624,10 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z14">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA14">
         <v>2</v>
@@ -3131,10 +3131,10 @@
         <v>1.49</v>
       </c>
       <c r="AE17">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AG17">
         <v>1.65</v>
@@ -3153,7 +3153,7 @@
         <v>1.03</v>
       </c>
       <c r="AK17">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,16 +3252,16 @@
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="R18">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="S18">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T18">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="U18">
         <v>3.1</v>
@@ -3297,10 +3297,10 @@
         <v>1</v>
       </c>
       <c r="AF18">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG18">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3415,13 +3415,13 @@
         <v>4</v>
       </c>
       <c r="Q19">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R19">
         <v>2</v>
       </c>
       <c r="S19">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T19">
         <v>2.6</v>
@@ -3575,10 +3575,10 @@
         <v>3</v>
       </c>
       <c r="P20">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q20">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="R20">
         <v>2.05</v>
@@ -3608,7 +3608,7 @@
         <v>2.7</v>
       </c>
       <c r="AA20">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AB20">
         <v>1.61</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK20">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3735,16 +3735,16 @@
         <v>1.75</v>
       </c>
       <c r="O21">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P21">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="Q21">
         <v>2.38</v>
       </c>
       <c r="R21">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S21">
         <v>1.38</v>
@@ -3759,7 +3759,7 @@
         <v>1.44</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3777,7 +3777,7 @@
         <v>1.8</v>
       </c>
       <c r="AC21">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AD21">
         <v>1.28</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK21">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4438,10 +4438,10 @@
         <v>1.02</v>
       </c>
       <c r="AF25">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG25">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z27">
         <v>2.83</v>
@@ -4764,10 +4764,10 @@
         <v>1.01</v>
       </c>
       <c r="AF27">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG27">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AK27">
         <v>1.74</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="O13">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="P13">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="Q13">
-        <v>2.81</v>
+        <v>2.64</v>
       </c>
       <c r="R13">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="S13">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="T13">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="U13">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="V13">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W13">
         <v>1.03</v>
@@ -2461,31 +2461,31 @@
         <v>1.1</v>
       </c>
       <c r="Y13">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="Z13">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AA13">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AB13">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AC13">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AD13">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE13">
         <v>1.02</v>
       </c>
       <c r="AF13">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="AG13">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AK13">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="O22">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P22">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AA22">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB22">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O23">
         <v>2.9</v>
       </c>
       <c r="P23">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q23">
         <v>3.07</v>
@@ -4079,10 +4079,10 @@
         <v>2.38</v>
       </c>
       <c r="U23">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="V23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W23">
         <v>1.04</v>
@@ -4399,7 +4399,7 @@
         <v>2</v>
       </c>
       <c r="S25">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T25">
         <v>2.6</v>
@@ -4411,7 +4411,7 @@
         <v>1.29</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
         <v>1.03</v>
@@ -4420,7 +4420,7 @@
         <v>1.36</v>
       </c>
       <c r="Z25">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AA25">
         <v>2.25</v>
@@ -4432,7 +4432,7 @@
         <v>4</v>
       </c>
       <c r="AD25">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE25">
         <v>1.02</v>
@@ -4457,7 +4457,7 @@
         <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4562,7 +4562,7 @@
         <v>2.1</v>
       </c>
       <c r="S26">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T26">
         <v>2.8</v>
@@ -4586,10 +4586,10 @@
         <v>3.14</v>
       </c>
       <c r="AA26">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AB26">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC26">
         <v>3.28</v>
@@ -4728,7 +4728,7 @@
         <v>1.46</v>
       </c>
       <c r="T27">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="U27">
         <v>3.4</v>
@@ -4749,7 +4749,7 @@
         <v>2.83</v>
       </c>
       <c r="AA27">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AB27">
         <v>1.61</v>
@@ -4764,7 +4764,7 @@
         <v>1.01</v>
       </c>
       <c r="AF27">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG27">
         <v>1.8</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK27">
         <v>1.74</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O22">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="P22">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="Q22">
         <v>3.2</v>
@@ -3910,40 +3910,40 @@
         <v>1.92</v>
       </c>
       <c r="S22">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T22">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="U22">
         <v>2.9</v>
       </c>
       <c r="V22">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W22">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
         <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z22">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="AA22">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AB22">
         <v>1.65</v>
       </c>
       <c r="AC22">
-        <v>3.78</v>
+        <v>3.91</v>
       </c>
       <c r="AD22">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE22">
         <v>1.03</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK22">
         <v>1.45</v>
@@ -4423,7 +4423,7 @@
         <v>2.69</v>
       </c>
       <c r="AA25">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB25">
         <v>1.6</v>
@@ -4432,7 +4432,7 @@
         <v>4</v>
       </c>
       <c r="AD25">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE25">
         <v>1.02</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="O26">
         <v>3.2</v>
@@ -4556,13 +4556,13 @@
         <v>2.46</v>
       </c>
       <c r="Q26">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="R26">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="S26">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T26">
         <v>2.8</v>
@@ -4571,10 +4571,10 @@
         <v>2.97</v>
       </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4589,7 +4589,7 @@
         <v>2.05</v>
       </c>
       <c r="AB26">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC26">
         <v>3.28</v>
@@ -4601,10 +4601,10 @@
         <v>1.05</v>
       </c>
       <c r="AF26">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG26">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>2.83</v>
       </c>
       <c r="AA27">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AB27">
         <v>1.61</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -1314,7 +1314,7 @@
         <v>1.35</v>
       </c>
       <c r="W6">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
         <v>1.01</v>
@@ -1329,13 +1329,13 @@
         <v>2.03</v>
       </c>
       <c r="AB6">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC6">
-        <v>3.61</v>
+        <v>3.8</v>
       </c>
       <c r="AD6">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE6">
         <v>1.04</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="O9">
         <v>3.2</v>
       </c>
       <c r="P9">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -2606,10 +2606,10 @@
         <v>2.05</v>
       </c>
       <c r="S14">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T14">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="U14">
         <v>3.03</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK14">
         <v>2</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="O15">
         <v>3.35</v>
       </c>
       <c r="P15">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2920,7 +2920,7 @@
         <v>2.2</v>
       </c>
       <c r="O16">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P16">
         <v>2.95</v>
@@ -2944,10 +2944,10 @@
         <v>1.26</v>
       </c>
       <c r="W16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y16">
         <v>1.38</v>
@@ -2956,10 +2956,10 @@
         <v>2.91</v>
       </c>
       <c r="AA16">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AB16">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC16">
         <v>4.15</v>
@@ -2968,13 +2968,13 @@
         <v>1.16</v>
       </c>
       <c r="AE16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF16">
         <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3089,22 +3089,22 @@
         <v>11</v>
       </c>
       <c r="Q17">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="R17">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T17">
         <v>3.18</v>
       </c>
       <c r="U17">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V17">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W17">
         <v>1.09</v>
@@ -3119,13 +3119,13 @@
         <v>4.55</v>
       </c>
       <c r="AA17">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB17">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="AC17">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AD17">
         <v>1.49</v>
@@ -3134,7 +3134,7 @@
         <v>1.17</v>
       </c>
       <c r="AF17">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AG17">
         <v>1.65</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AK17">
         <v>3.62</v>
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="R18">
         <v>1.85</v>
@@ -3276,13 +3276,13 @@
         <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z18">
         <v>2.62</v>
       </c>
       <c r="AA18">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="AB18">
         <v>1.53</v>
@@ -3300,7 +3300,7 @@
         <v>1.92</v>
       </c>
       <c r="AG18">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AK18">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="O19">
         <v>3</v>
       </c>
       <c r="P19">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q19">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="R19">
         <v>2</v>
@@ -3424,13 +3424,13 @@
         <v>1.47</v>
       </c>
       <c r="T19">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U19">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="V19">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W19">
         <v>1.02</v>
@@ -3460,10 +3460,10 @@
         <v>1.01</v>
       </c>
       <c r="AF19">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AG19">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
         <v>1.73</v>
@@ -3584,16 +3584,16 @@
         <v>2.05</v>
       </c>
       <c r="S20">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T20">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="U20">
         <v>3.2</v>
       </c>
       <c r="V20">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W20">
         <v>1.05</v>
@@ -3608,10 +3608,10 @@
         <v>2.7</v>
       </c>
       <c r="AA20">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB20">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC20">
         <v>3.92</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3735,22 +3735,22 @@
         <v>1.75</v>
       </c>
       <c r="O21">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
         <v>4</v>
       </c>
       <c r="Q21">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="R21">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="S21">
         <v>1.38</v>
       </c>
       <c r="T21">
-        <v>2.64</v>
+        <v>2.91</v>
       </c>
       <c r="U21">
         <v>2.5</v>
@@ -3765,16 +3765,16 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z21">
         <v>3.28</v>
       </c>
       <c r="AA21">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AB21">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC21">
         <v>3.05</v>
@@ -3786,10 +3786,10 @@
         <v>1.07</v>
       </c>
       <c r="AF21">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG21">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O12">
         <v>3.25</v>
       </c>
       <c r="P12">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>3.2</v>
       </c>
       <c r="R22">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S22">
         <v>1.36</v>
@@ -3925,34 +3925,34 @@
         <v>1.07</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y22">
         <v>1.37</v>
       </c>
       <c r="Z22">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AA22">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB22">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC22">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="AD22">
         <v>1.23</v>
       </c>
       <c r="AE22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG22">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.35</v>
       </c>
       <c r="AK22">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="O26">
         <v>3.2</v>
       </c>
       <c r="P26">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="Q26">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="R26">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="S26">
         <v>1.39</v>
@@ -4580,10 +4580,10 @@
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z26">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA26">
         <v>2.05</v>
@@ -4592,19 +4592,19 @@
         <v>1.78</v>
       </c>
       <c r="AC26">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AD26">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE26">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG26">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.44</v>
       </c>
       <c r="AK26">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL26">
         <v>0</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -1296,16 +1296,16 @@
         <v>3</v>
       </c>
       <c r="Q6">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="R6">
         <v>1.99</v>
       </c>
       <c r="S6">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="T6">
-        <v>2.57</v>
+        <v>2.42</v>
       </c>
       <c r="U6">
         <v>3</v>
@@ -1317,16 +1317,16 @@
         <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z6">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AA6">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AB6">
         <v>1.72</v>
@@ -2600,7 +2600,7 @@
         <v>4.75</v>
       </c>
       <c r="Q14">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="R14">
         <v>2.05</v>
@@ -2609,10 +2609,10 @@
         <v>1.4</v>
       </c>
       <c r="T14">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="U14">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="V14">
         <v>1.36</v>
@@ -2630,10 +2630,10 @@
         <v>3.08</v>
       </c>
       <c r="AA14">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB14">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC14">
         <v>3.6</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK14">
         <v>2</v>
@@ -3406,25 +3406,25 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="O19">
         <v>3</v>
       </c>
       <c r="P19">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q19">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="R19">
         <v>2</v>
       </c>
       <c r="S19">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T19">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U19">
         <v>3.12</v>
@@ -3433,37 +3433,37 @@
         <v>1.28</v>
       </c>
       <c r="W19">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z19">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AA19">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AB19">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC19">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="AD19">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE19">
         <v>1.01</v>
       </c>
       <c r="AF19">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AG19">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK19">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="O20">
         <v>3</v>
@@ -3581,16 +3581,16 @@
         <v>2.88</v>
       </c>
       <c r="R20">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="S20">
         <v>1.44</v>
       </c>
       <c r="T20">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="U20">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="V20">
         <v>1.33</v>
@@ -3608,25 +3608,25 @@
         <v>2.7</v>
       </c>
       <c r="AA20">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB20">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC20">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="AD20">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE20">
         <v>1.02</v>
       </c>
       <c r="AF20">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AG20">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3747,10 +3747,10 @@
         <v>2.03</v>
       </c>
       <c r="S21">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
-        <v>2.91</v>
+        <v>2.64</v>
       </c>
       <c r="U21">
         <v>2.5</v>
@@ -3759,7 +3759,7 @@
         <v>1.44</v>
       </c>
       <c r="W21">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3771,7 +3771,7 @@
         <v>3.28</v>
       </c>
       <c r="AA21">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB21">
         <v>1.9</v>
@@ -3789,7 +3789,7 @@
         <v>1.77</v>
       </c>
       <c r="AG21">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK21">
         <v>1.87</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -1296,16 +1296,16 @@
         <v>3</v>
       </c>
       <c r="Q6">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="R6">
         <v>1.99</v>
       </c>
       <c r="S6">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T6">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="U6">
         <v>3</v>
@@ -1326,7 +1326,7 @@
         <v>2.97</v>
       </c>
       <c r="AA6">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AB6">
         <v>1.72</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>2.13</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2600,7 +2600,7 @@
         <v>4.75</v>
       </c>
       <c r="Q14">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="R14">
         <v>2.05</v>
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="O16">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P16">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="Q16">
-        <v>2.75</v>
+        <v>3.06</v>
       </c>
       <c r="R16">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="S16">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="T16">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="U16">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="V16">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W16">
         <v>1.03</v>
@@ -2950,19 +2950,19 @@
         <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z16">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="AA16">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AB16">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AC16">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AD16">
         <v>1.16</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK16">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="O17">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="P17">
         <v>11</v>
@@ -3092,7 +3092,7 @@
         <v>1.67</v>
       </c>
       <c r="R17">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S17">
         <v>1.27</v>
@@ -3104,13 +3104,13 @@
         <v>2.29</v>
       </c>
       <c r="V17">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W17">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17">
         <v>1.13</v>
@@ -3119,22 +3119,22 @@
         <v>4.55</v>
       </c>
       <c r="AA17">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB17">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AC17">
         <v>2.34</v>
       </c>
       <c r="AD17">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AE17">
         <v>1.17</v>
       </c>
       <c r="AF17">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AG17">
         <v>1.65</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK17">
         <v>3.62</v>
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>3.07</v>
+        <v>3.02</v>
       </c>
       <c r="R18">
         <v>1.85</v>
@@ -3282,7 +3282,7 @@
         <v>2.62</v>
       </c>
       <c r="AA18">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="AB18">
         <v>1.53</v>
@@ -3297,7 +3297,7 @@
         <v>1</v>
       </c>
       <c r="AF18">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AG18">
         <v>1.73</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK18">
         <v>1.5</v>
@@ -3581,13 +3581,13 @@
         <v>2.88</v>
       </c>
       <c r="R20">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S20">
         <v>1.44</v>
       </c>
       <c r="T20">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="U20">
         <v>3.18</v>
@@ -3608,7 +3608,7 @@
         <v>2.7</v>
       </c>
       <c r="AA20">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AB20">
         <v>1.59</v>
@@ -3623,10 +3623,10 @@
         <v>1.02</v>
       </c>
       <c r="AF20">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG20">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3738,7 +3738,7 @@
         <v>3.4</v>
       </c>
       <c r="P21">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q21">
         <v>2.35</v>
@@ -3786,10 +3786,10 @@
         <v>1.07</v>
       </c>
       <c r="AF21">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG21">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.29</v>
       </c>
       <c r="AK21">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4384,46 +4384,46 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
         <v>4.4</v>
       </c>
       <c r="Q25">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R25">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S25">
         <v>1.43</v>
       </c>
       <c r="T25">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="U25">
         <v>3.3</v>
       </c>
       <c r="V25">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y25">
         <v>1.36</v>
       </c>
       <c r="Z25">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AA25">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AB25">
         <v>1.6</v>
@@ -4432,7 +4432,7 @@
         <v>4</v>
       </c>
       <c r="AD25">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE25">
         <v>1.02</v>
@@ -4457,7 +4457,7 @@
         <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4710,31 +4710,31 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="O27">
+        <v>3.1</v>
+      </c>
+      <c r="P27">
         <v>3.3</v>
       </c>
-      <c r="P27">
-        <v>3.65</v>
-      </c>
       <c r="Q27">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="R27">
         <v>1.88</v>
       </c>
       <c r="S27">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T27">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="U27">
         <v>3.4</v>
       </c>
       <c r="V27">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W27">
         <v>1.03</v>
@@ -4743,13 +4743,13 @@
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z27">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="AA27">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AB27">
         <v>1.61</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK27">
         <v>1.74</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="O3">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1296,16 +1296,16 @@
         <v>3</v>
       </c>
       <c r="Q6">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="R6">
         <v>1.99</v>
       </c>
       <c r="S6">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T6">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="U6">
         <v>3</v>
@@ -1326,7 +1326,7 @@
         <v>2.97</v>
       </c>
       <c r="AA6">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AB6">
         <v>1.72</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="O9">
         <v>3.2</v>
       </c>
       <c r="P9">
+        <v>3.2</v>
+      </c>
+      <c r="Q9">
+        <v>2.72</v>
+      </c>
+      <c r="R9">
+        <v>2.1</v>
+      </c>
+      <c r="S9">
+        <v>1.38</v>
+      </c>
+      <c r="T9">
+        <v>2.8</v>
+      </c>
+      <c r="U9">
+        <v>2.85</v>
+      </c>
+      <c r="V9">
+        <v>1.36</v>
+      </c>
+      <c r="W9">
+        <v>1.05</v>
+      </c>
+      <c r="X9">
+        <v>1.03</v>
+      </c>
+      <c r="Y9">
+        <v>1.3</v>
+      </c>
+      <c r="Z9">
         <v>3</v>
       </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         <v>2.13</v>
       </c>
       <c r="Q12">
-        <v>3.79</v>
+        <v>3.62</v>
       </c>
       <c r="R12">
         <v>2.04</v>
@@ -2295,7 +2295,7 @@
         <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
         <v>1.24</v>
@@ -2310,10 +2310,10 @@
         <v>1.82</v>
       </c>
       <c r="AC12">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AD12">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
         <v>1.06</v>
@@ -2322,7 +2322,7 @@
         <v>1.68</v>
       </c>
       <c r="AG12">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2431,13 +2431,13 @@
         <v>1.83</v>
       </c>
       <c r="O13">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P13">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="Q13">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="R13">
         <v>1.83</v>
@@ -2449,31 +2449,31 @@
         <v>2.21</v>
       </c>
       <c r="U13">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="V13">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y13">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Z13">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AA13">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AB13">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC13">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AD13">
         <v>1.08</v>
@@ -2482,10 +2482,10 @@
         <v>1.02</v>
       </c>
       <c r="AF13">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AG13">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AK13">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,7 +2600,7 @@
         <v>4.75</v>
       </c>
       <c r="Q14">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="R14">
         <v>2.05</v>
@@ -2630,7 +2630,7 @@
         <v>3.08</v>
       </c>
       <c r="AA14">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB14">
         <v>1.75</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AK14">
         <v>2</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="O15">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
         <v>3.7</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2956,7 +2956,7 @@
         <v>2.92</v>
       </c>
       <c r="AA16">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AB16">
         <v>1.58</v>
@@ -2974,7 +2974,7 @@
         <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q18">
-        <v>3.02</v>
+        <v>1.65</v>
       </c>
       <c r="R18">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="S18">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="T18">
-        <v>2.32</v>
+        <v>3.18</v>
       </c>
       <c r="U18">
-        <v>3.1</v>
+        <v>2.29</v>
       </c>
       <c r="V18">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X18">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="Z18">
-        <v>2.62</v>
+        <v>4.55</v>
       </c>
       <c r="AA18">
-        <v>2.28</v>
+        <v>1.57</v>
       </c>
       <c r="AB18">
-        <v>1.53</v>
+        <v>2.33</v>
       </c>
       <c r="AC18">
-        <v>4.3</v>
+        <v>2.33</v>
       </c>
       <c r="AD18">
-        <v>1.15</v>
+        <v>1.51</v>
       </c>
       <c r="AE18">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AF18">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG18">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="AK18">
-        <v>1.5</v>
+        <v>3.64</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>2.75</v>
       </c>
       <c r="Q22">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="R22">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S22">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T22">
         <v>2.75</v>
       </c>
       <c r="U22">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="V22">
         <v>1.35</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
         <v>1.37</v>
       </c>
       <c r="Z22">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="AA22">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB22">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC22">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="AD22">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE22">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG22">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.35</v>
       </c>
       <c r="AK22">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4061,13 +4061,13 @@
         <v>2.4</v>
       </c>
       <c r="O23">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P23">
         <v>3.1</v>
       </c>
       <c r="Q23">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="R23">
         <v>1.9</v>
@@ -4091,31 +4091,31 @@
         <v>1.08</v>
       </c>
       <c r="Y23">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Z23">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AA23">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="AB23">
         <v>1.42</v>
       </c>
       <c r="AC23">
-        <v>5.45</v>
+        <v>5.54</v>
       </c>
       <c r="AD23">
         <v>1.1</v>
       </c>
       <c r="AE23">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF23">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AG23">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4384,25 +4384,25 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O25">
         <v>3.3</v>
       </c>
       <c r="P25">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q25">
         <v>2.4</v>
       </c>
       <c r="R25">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S25">
         <v>1.43</v>
       </c>
       <c r="T25">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="U25">
         <v>3.3</v>
@@ -4423,7 +4423,7 @@
         <v>2.7</v>
       </c>
       <c r="AA25">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AB25">
         <v>1.6</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="O26">
         <v>3.2</v>
       </c>
       <c r="P26">
-        <v>2.37</v>
+        <v>2.46</v>
       </c>
       <c r="Q26">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="R26">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S26">
         <v>1.39</v>
@@ -4568,22 +4568,22 @@
         <v>2.8</v>
       </c>
       <c r="U26">
-        <v>2.97</v>
+        <v>2.77</v>
       </c>
       <c r="V26">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z26">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="AA26">
         <v>2.05</v>
@@ -4592,19 +4592,19 @@
         <v>1.78</v>
       </c>
       <c r="AC26">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="AD26">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AE26">
         <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.44</v>
       </c>
       <c r="AK26">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         <v>3.1</v>
       </c>
       <c r="P27">
-        <v>3.3</v>
+        <v>3.07</v>
       </c>
       <c r="Q27">
         <v>2.58</v>
@@ -4749,7 +4749,7 @@
         <v>2.82</v>
       </c>
       <c r="AA27">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AB27">
         <v>1.61</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="O12">
         <v>3.25</v>
@@ -2274,7 +2274,7 @@
         <v>2.13</v>
       </c>
       <c r="Q12">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="R12">
         <v>2.04</v>
@@ -2295,7 +2295,7 @@
         <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
         <v>1.24</v>
@@ -2319,10 +2319,10 @@
         <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AK12">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2431,13 +2431,13 @@
         <v>1.83</v>
       </c>
       <c r="O13">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="P13">
         <v>3.35</v>
       </c>
       <c r="Q13">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="R13">
         <v>1.83</v>
@@ -2455,10 +2455,10 @@
         <v>1.22</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Y13">
         <v>1.58</v>
@@ -2501,7 +2501,7 @@
         <v>1.29</v>
       </c>
       <c r="AK13">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2926,7 +2926,7 @@
         <v>3.05</v>
       </c>
       <c r="Q16">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="R16">
         <v>1.95</v>
@@ -2953,13 +2953,13 @@
         <v>1.4</v>
       </c>
       <c r="Z16">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="AA16">
         <v>2.24</v>
       </c>
       <c r="AB16">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC16">
         <v>4.5</v>
@@ -2974,7 +2974,7 @@
         <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3089,55 +3089,55 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3264,10 +3264,10 @@
         <v>3.18</v>
       </c>
       <c r="U18">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="V18">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W18">
         <v>1.12</v>
@@ -3300,7 +3300,7 @@
         <v>2.05</v>
       </c>
       <c r="AG18">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="O19">
         <v>3</v>
@@ -3445,10 +3445,10 @@
         <v>2.88</v>
       </c>
       <c r="AA19">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB19">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC19">
         <v>4.33</v>
@@ -3587,7 +3587,7 @@
         <v>1.44</v>
       </c>
       <c r="T20">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="U20">
         <v>3.18</v>
@@ -3735,16 +3735,16 @@
         <v>1.75</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P21">
         <v>3.9</v>
       </c>
       <c r="Q21">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="R21">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="S21">
         <v>1.4</v>
@@ -3771,13 +3771,13 @@
         <v>3.28</v>
       </c>
       <c r="AA21">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB21">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC21">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AD21">
         <v>1.28</v>
@@ -3786,10 +3786,10 @@
         <v>1.07</v>
       </c>
       <c r="AF21">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG21">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.29</v>
       </c>
       <c r="AK21">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>1.42</v>
       </c>
       <c r="T22">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="U22">
         <v>2.95</v>
@@ -3922,28 +3922,28 @@
         <v>1.35</v>
       </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="Z22">
-        <v>2.99</v>
+        <v>2.86</v>
       </c>
       <c r="AA22">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AB22">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC22">
         <v>3.86</v>
       </c>
       <c r="AD22">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE22">
         <v>1.02</v>
@@ -3968,7 +3968,7 @@
         <v>1.35</v>
       </c>
       <c r="AK22">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4387,22 +4387,22 @@
         <v>1.67</v>
       </c>
       <c r="O25">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
         <v>4.5</v>
       </c>
       <c r="Q25">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R25">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T25">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U25">
         <v>3.3</v>
@@ -4411,25 +4411,25 @@
         <v>1.3</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y25">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z25">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AA25">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AB25">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC25">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="AD25">
         <v>1.18</v>
@@ -4438,10 +4438,10 @@
         <v>1.02</v>
       </c>
       <c r="AF25">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AG25">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4595,16 +4595,16 @@
         <v>3.43</v>
       </c>
       <c r="AD26">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE26">
         <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG26">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4719,10 +4719,10 @@
         <v>3.07</v>
       </c>
       <c r="Q27">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="R27">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="S27">
         <v>1.47</v>
@@ -4749,7 +4749,7 @@
         <v>2.82</v>
       </c>
       <c r="AA27">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AB27">
         <v>1.61</v>
@@ -4783,7 +4783,7 @@
         <v>1.17</v>
       </c>
       <c r="AK27">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="O19">
         <v>3</v>
@@ -3415,7 +3415,7 @@
         <v>3.6</v>
       </c>
       <c r="Q19">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R19">
         <v>2</v>
@@ -3424,7 +3424,7 @@
         <v>1.48</v>
       </c>
       <c r="T19">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="U19">
         <v>3.12</v>
@@ -3433,10 +3433,10 @@
         <v>1.28</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y19">
         <v>1.4</v>
@@ -3454,16 +3454,16 @@
         <v>4.33</v>
       </c>
       <c r="AD19">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE19">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF19">
         <v>1.97</v>
       </c>
       <c r="AG19">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3575,10 +3575,10 @@
         <v>3</v>
       </c>
       <c r="P20">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="Q20">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="R20">
         <v>2.06</v>
@@ -3593,13 +3593,13 @@
         <v>3.18</v>
       </c>
       <c r="V20">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="W20">
         <v>1.05</v>
       </c>
       <c r="X20">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y20">
         <v>1.36</v>
@@ -3608,16 +3608,16 @@
         <v>2.7</v>
       </c>
       <c r="AA20">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AB20">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC20">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="AD20">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE20">
         <v>1.02</v>
@@ -3626,7 +3626,7 @@
         <v>1.9</v>
       </c>
       <c r="AG20">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK20">
         <v>1.6</v>
@@ -3741,7 +3741,7 @@
         <v>3.9</v>
       </c>
       <c r="Q21">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="R21">
         <v>2.02</v>
@@ -3753,13 +3753,13 @@
         <v>2.64</v>
       </c>
       <c r="U21">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="V21">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3771,10 +3771,10 @@
         <v>3.28</v>
       </c>
       <c r="AA21">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB21">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC21">
         <v>3.08</v>
@@ -3789,7 +3789,7 @@
         <v>1.77</v>
       </c>
       <c r="AG21">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
         <v>1.85</v>
@@ -4402,19 +4402,19 @@
         <v>1.42</v>
       </c>
       <c r="T25">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U25">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="V25">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W25">
         <v>1.04</v>
       </c>
       <c r="X25">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
         <v>1.35</v>
@@ -4432,7 +4432,7 @@
         <v>3.92</v>
       </c>
       <c r="AD25">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE25">
         <v>1.02</v>
@@ -4457,7 +4457,7 @@
         <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4713,43 +4713,43 @@
         <v>2</v>
       </c>
       <c r="O27">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P27">
-        <v>3.07</v>
+        <v>3.5</v>
       </c>
       <c r="Q27">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="R27">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="S27">
         <v>1.47</v>
       </c>
       <c r="T27">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="U27">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="V27">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W27">
         <v>1.03</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y27">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z27">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="AA27">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AB27">
         <v>1.61</v>
@@ -4758,13 +4758,13 @@
         <v>4.4</v>
       </c>
       <c r="AD27">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE27">
         <v>1.01</v>
       </c>
       <c r="AF27">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG27">
         <v>1.8</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK27">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="O3">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P3">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q3">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R3">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S3">
         <v>1.36</v>
@@ -819,7 +819,7 @@
         <v>2.88</v>
       </c>
       <c r="U3">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="V3">
         <v>1.36</v>
@@ -831,31 +831,31 @@
         <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z3">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA3">
+        <v>2.05</v>
+      </c>
+      <c r="AB3">
+        <v>1.75</v>
+      </c>
+      <c r="AC3">
+        <v>3.34</v>
+      </c>
+      <c r="AD3">
+        <v>1.24</v>
+      </c>
+      <c r="AE3">
+        <v>1.06</v>
+      </c>
+      <c r="AF3">
         <v>2</v>
       </c>
-      <c r="AB3">
+      <c r="AG3">
         <v>1.73</v>
-      </c>
-      <c r="AC3">
-        <v>3.8</v>
-      </c>
-      <c r="AD3">
-        <v>1.22</v>
-      </c>
-      <c r="AE3">
-        <v>1.05</v>
-      </c>
-      <c r="AF3">
-        <v>2.07</v>
-      </c>
-      <c r="AG3">
-        <v>1.72</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,34 +961,34 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="O4">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="P4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q4">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="R4">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="S4">
         <v>1.24</v>
       </c>
       <c r="T4">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U4">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V4">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="W4">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X4">
         <v>1.01</v>
@@ -1000,25 +1000,25 @@
         <v>4.9</v>
       </c>
       <c r="AA4">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB4">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC4">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD4">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE4">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AF4">
         <v>2.3</v>
       </c>
       <c r="AG4">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AK4">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1314,7 +1314,7 @@
         <v>1.35</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
         <v>1.03</v>
@@ -1332,10 +1332,10 @@
         <v>1.72</v>
       </c>
       <c r="AC6">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="AD6">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE6">
         <v>1.04</v>
@@ -1450,61 +1450,61 @@
         </is>
       </c>
       <c r="N7">
+        <v>2</v>
+      </c>
+      <c r="O7">
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <v>3.5</v>
+      </c>
+      <c r="Q7">
+        <v>2.51</v>
+      </c>
+      <c r="R7">
         <v>2.06</v>
       </c>
-      <c r="O7">
-        <v>3.13</v>
-      </c>
-      <c r="P7">
-        <v>3.68</v>
-      </c>
-      <c r="Q7">
-        <v>2.67</v>
-      </c>
-      <c r="R7">
-        <v>1.98</v>
-      </c>
       <c r="S7">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T7">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U7">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="V7">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z7">
         <v>2.81</v>
       </c>
       <c r="AA7">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="AB7">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC7">
-        <v>4.5</v>
+        <v>4.04</v>
       </c>
       <c r="AD7">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE7">
         <v>1.02</v>
       </c>
       <c r="AF7">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG7">
         <v>1.8</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK7">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="O8">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P8">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q8">
         <v>2.82</v>
@@ -1634,10 +1634,10 @@
         <v>2.6</v>
       </c>
       <c r="U8">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="V8">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W8">
         <v>1.03</v>
@@ -1652,7 +1652,7 @@
         <v>2.65</v>
       </c>
       <c r="AA8">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB8">
         <v>1.57</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
         <v>1.65</v>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="O9">
         <v>3.2</v>
       </c>
       <c r="P9">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q9">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="R9">
         <v>2.1</v>
@@ -1809,25 +1809,25 @@
         <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z9">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AA9">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AB9">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AC9">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD9">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE9">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF9">
         <v>1.85</v>
@@ -1849,7 +1849,7 @@
         <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="O10">
-        <v>4.7</v>
+        <v>6.75</v>
       </c>
       <c r="P10">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="Q10">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="R10">
         <v>2.75</v>
       </c>
       <c r="S10">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T10">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U10">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W10">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z10">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AA10">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB10">
         <v>2.37</v>
       </c>
       <c r="AC10">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AD10">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AE10">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF10">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AG10">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AK10">
         <v>4.7</v>
@@ -2114,19 +2114,19 @@
         <v>3.2</v>
       </c>
       <c r="R11">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S11">
         <v>1.41</v>
       </c>
       <c r="T11">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U11">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="V11">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W11">
         <v>1.04</v>
@@ -2138,13 +2138,13 @@
         <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA11">
         <v>2.1</v>
       </c>
       <c r="AB11">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC11">
         <v>4</v>
@@ -2156,7 +2156,7 @@
         <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AG11">
         <v>1.84</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="O12">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q12">
         <v>3.5</v>
@@ -2316,7 +2316,7 @@
         <v>1.33</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
         <v>1.73</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AK12">
         <v>1.33</v>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="O13">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="P13">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="Q13">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="R13">
         <v>1.83</v>
@@ -2449,7 +2449,7 @@
         <v>2.21</v>
       </c>
       <c r="U13">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="V13">
         <v>1.22</v>
@@ -2461,10 +2461,10 @@
         <v>1.13</v>
       </c>
       <c r="Y13">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z13">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AA13">
         <v>2.9</v>
@@ -2473,19 +2473,19 @@
         <v>1.36</v>
       </c>
       <c r="AC13">
-        <v>5.45</v>
+        <v>6.5</v>
       </c>
       <c r="AD13">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AE13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF13">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AG13">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK13">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,10 +2600,10 @@
         <v>4.75</v>
       </c>
       <c r="Q14">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="R14">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S14">
         <v>1.4</v>
@@ -2612,7 +2612,7 @@
         <v>2.67</v>
       </c>
       <c r="U14">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="V14">
         <v>1.36</v>
@@ -2624,19 +2624,19 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z14">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA14">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AB14">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC14">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AD14">
         <v>1.25</v>
@@ -2648,7 +2648,7 @@
         <v>1.85</v>
       </c>
       <c r="AG14">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK14">
         <v>2</v>
@@ -2754,61 +2754,61 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="O15">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P15">
-        <v>3.7</v>
+        <v>3.83</v>
       </c>
       <c r="Q15">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="R15">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S15">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T15">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U15">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z15">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="AA15">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AB15">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AC15">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AD15">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE15">
         <v>1.1</v>
       </c>
       <c r="AF15">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG15">
         <v>1.95</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="O16">
         <v>3.05</v>
@@ -2926,7 +2926,7 @@
         <v>3.05</v>
       </c>
       <c r="Q16">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="R16">
         <v>1.95</v>
@@ -2935,7 +2935,7 @@
         <v>1.51</v>
       </c>
       <c r="T16">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="U16">
         <v>3</v>
@@ -2953,13 +2953,13 @@
         <v>1.4</v>
       </c>
       <c r="Z16">
-        <v>2.91</v>
+        <v>2.62</v>
       </c>
       <c r="AA16">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AB16">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC16">
         <v>4.5</v>
@@ -2968,13 +2968,13 @@
         <v>1.16</v>
       </c>
       <c r="AE16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF16">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG16">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK16">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,28 +3080,28 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q17">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="R17">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="S17">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T17">
         <v>2.32</v>
       </c>
       <c r="U17">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="V17">
         <v>1.3</v>
@@ -3110,34 +3110,34 @@
         <v>1.05</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z17">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="AA17">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AB17">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC17">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AD17">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE17">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AG17">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.28</v>
       </c>
       <c r="AK17">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3246,16 +3246,16 @@
         <v>1.25</v>
       </c>
       <c r="O18">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>11</v>
       </c>
       <c r="Q18">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="R18">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="S18">
         <v>1.27</v>
@@ -3279,28 +3279,28 @@
         <v>1.13</v>
       </c>
       <c r="Z18">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="AA18">
         <v>1.57</v>
       </c>
       <c r="AB18">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC18">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AD18">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE18">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF18">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AG18">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AK18">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -4061,16 +4061,16 @@
         <v>2.4</v>
       </c>
       <c r="O23">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="P23">
         <v>3.1</v>
       </c>
       <c r="Q23">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="R23">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="S23">
         <v>1.55</v>
@@ -4091,19 +4091,19 @@
         <v>1.08</v>
       </c>
       <c r="Y23">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Z23">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AA23">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AB23">
         <v>1.42</v>
       </c>
       <c r="AC23">
-        <v>5.54</v>
+        <v>5.62</v>
       </c>
       <c r="AD23">
         <v>1.1</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="O5">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="P5">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA5">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB5">
         <v>1.65</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2265,49 +2265,49 @@
         </is>
       </c>
       <c r="N12">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="O12">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q12">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R12">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="U12">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="V12">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W12">
         <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z12">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="AA12">
+        <v>1.82</v>
+      </c>
+      <c r="AB12">
         <v>1.85</v>
-      </c>
-      <c r="AB12">
-        <v>1.82</v>
       </c>
       <c r="AC12">
         <v>3.25</v>
@@ -2316,13 +2316,13 @@
         <v>1.33</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG12">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AK12">
         <v>1.33</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="O22">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P22">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q22">
         <v>2.9</v>
       </c>
       <c r="R22">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S22">
         <v>1.42</v>
@@ -3916,16 +3916,16 @@
         <v>2.76</v>
       </c>
       <c r="U22">
-        <v>2.95</v>
+        <v>3.21</v>
       </c>
       <c r="V22">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W22">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
         <v>1.34</v>
@@ -3934,19 +3934,19 @@
         <v>2.86</v>
       </c>
       <c r="AA22">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="AB22">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AC22">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="AD22">
         <v>1.19</v>
       </c>
       <c r="AE22">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF22">
         <v>1.83</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK22">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O26">
         <v>3.2</v>
@@ -4562,13 +4562,13 @@
         <v>1.98</v>
       </c>
       <c r="S26">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T26">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="U26">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="V26">
         <v>1.36</v>
@@ -4586,25 +4586,25 @@
         <v>3.11</v>
       </c>
       <c r="AA26">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB26">
         <v>1.78</v>
       </c>
       <c r="AC26">
-        <v>3.43</v>
+        <v>3.34</v>
       </c>
       <c r="AD26">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE26">
         <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AK26">
         <v>1.4</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="O3">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P3">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q3">
         <v>2.2</v>
       </c>
       <c r="R3">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="U3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>2.97</v>
+        <v>3.34</v>
       </c>
       <c r="AA3">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB3">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC3">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="AD3">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AE3">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF3">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="O4">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q4">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="R4">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="S4">
         <v>1.24</v>
       </c>
       <c r="T4">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U4">
         <v>2.25</v>
@@ -1003,7 +1003,7 @@
         <v>1.47</v>
       </c>
       <c r="AB4">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="AC4">
         <v>2.25</v>
@@ -1012,13 +1012,13 @@
         <v>1.57</v>
       </c>
       <c r="AE4">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AF4">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AG4">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AK4">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.35</v>
+        <v>2.98</v>
       </c>
       <c r="O6">
         <v>3.05</v>
       </c>
       <c r="P6">
-        <v>3</v>
+        <v>2.51</v>
       </c>
       <c r="Q6">
-        <v>3.12</v>
+        <v>3.88</v>
       </c>
       <c r="R6">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="S6">
         <v>1.48</v>
@@ -1308,10 +1308,10 @@
         <v>2.42</v>
       </c>
       <c r="U6">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
         <v>1.02</v>
@@ -1320,25 +1320,25 @@
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z6">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA6">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AB6">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AC6">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="AD6">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
         <v>1.83</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AK6">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O8">
         <v>3.1</v>
       </c>
       <c r="P8">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q8">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="R8">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="S8">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T8">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="U8">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="V8">
         <v>1.3</v>
       </c>
       <c r="W8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
+        <v>1.04</v>
+      </c>
+      <c r="Y8">
+        <v>1.31</v>
+      </c>
+      <c r="Z8">
+        <v>2.92</v>
+      </c>
+      <c r="AA8">
+        <v>2.15</v>
+      </c>
+      <c r="AB8">
+        <v>1.65</v>
+      </c>
+      <c r="AC8">
+        <v>3.72</v>
+      </c>
+      <c r="AD8">
+        <v>1.2</v>
+      </c>
+      <c r="AE8">
         <v>1.05</v>
       </c>
-      <c r="Y8">
-        <v>1.41</v>
-      </c>
-      <c r="Z8">
-        <v>2.65</v>
-      </c>
-      <c r="AA8">
-        <v>2.3</v>
-      </c>
-      <c r="AB8">
+      <c r="AF8">
+        <v>1.85</v>
+      </c>
+      <c r="AG8">
+        <v>1.85</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>1.3</v>
+      </c>
+      <c r="AK8">
         <v>1.57</v>
-      </c>
-      <c r="AC8">
-        <v>4.2</v>
-      </c>
-      <c r="AD8">
-        <v>1.17</v>
-      </c>
-      <c r="AE8">
-        <v>1.03</v>
-      </c>
-      <c r="AF8">
-        <v>1.95</v>
-      </c>
-      <c r="AG8">
-        <v>1.75</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.25</v>
-      </c>
-      <c r="AK8">
-        <v>1.65</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,22 +1785,22 @@
         <v>3.3</v>
       </c>
       <c r="Q9">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S9">
         <v>1.38</v>
       </c>
       <c r="T9">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U9">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W9">
         <v>1.05</v>
@@ -1809,13 +1809,13 @@
         <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z9">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AA9">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AB9">
         <v>1.71</v>
@@ -1824,13 +1824,13 @@
         <v>3.5</v>
       </c>
       <c r="AD9">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE9">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF9">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG9">
         <v>1.87</v>
@@ -1939,65 +1939,65 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="O10">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="P10">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="Q10">
+        <v>1.53</v>
+      </c>
+      <c r="R10">
+        <v>2.48</v>
+      </c>
+      <c r="S10">
+        <v>1.28</v>
+      </c>
+      <c r="T10">
+        <v>3.6</v>
+      </c>
+      <c r="U10">
+        <v>2.25</v>
+      </c>
+      <c r="V10">
+        <v>1.47</v>
+      </c>
+      <c r="W10">
+        <v>1.11</v>
+      </c>
+      <c r="X10">
+        <v>1.02</v>
+      </c>
+      <c r="Y10">
+        <v>1.18</v>
+      </c>
+      <c r="Z10">
+        <v>4.8</v>
+      </c>
+      <c r="AA10">
+        <v>1.57</v>
+      </c>
+      <c r="AB10">
+        <v>2.3</v>
+      </c>
+      <c r="AC10">
+        <v>2.51</v>
+      </c>
+      <c r="AD10">
         <v>1.44</v>
       </c>
-      <c r="R10">
-        <v>2.75</v>
-      </c>
-      <c r="S10">
-        <v>1.26</v>
-      </c>
-      <c r="T10">
-        <v>3.8</v>
-      </c>
-      <c r="U10">
-        <v>2.2</v>
-      </c>
-      <c r="V10">
-        <v>1.57</v>
-      </c>
-      <c r="W10">
-        <v>1.12</v>
-      </c>
-      <c r="X10">
-        <v>1.01</v>
-      </c>
-      <c r="Y10">
-        <v>1.15</v>
-      </c>
-      <c r="Z10">
-        <v>5.2</v>
-      </c>
-      <c r="AA10">
+      <c r="AE10">
+        <v>1.14</v>
+      </c>
+      <c r="AF10">
+        <v>2.4</v>
+      </c>
+      <c r="AG10">
         <v>1.5</v>
       </c>
-      <c r="AB10">
-        <v>2.37</v>
-      </c>
-      <c r="AC10">
-        <v>2.38</v>
-      </c>
-      <c r="AD10">
-        <v>1.51</v>
-      </c>
-      <c r="AE10">
-        <v>1.17</v>
-      </c>
-      <c r="AF10">
-        <v>2.6</v>
-      </c>
-      <c r="AG10">
-        <v>1.44</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK10">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,43 +2102,43 @@
         </is>
       </c>
       <c r="N11">
+        <v>2.53</v>
+      </c>
+      <c r="O11">
+        <v>3.06</v>
+      </c>
+      <c r="P11">
         <v>2.5</v>
       </c>
-      <c r="O11">
-        <v>3.2</v>
-      </c>
-      <c r="P11">
-        <v>2.6</v>
-      </c>
       <c r="Q11">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R11">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S11">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T11">
         <v>2.75</v>
       </c>
       <c r="U11">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V11">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W11">
         <v>1.04</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z11">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AA11">
         <v>2.1</v>
@@ -2147,16 +2147,16 @@
         <v>1.65</v>
       </c>
       <c r="AC11">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD11">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE11">
         <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG11">
         <v>1.84</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>4.75</v>
       </c>
       <c r="Q14">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="R14">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S14">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="T14">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
       <c r="U14">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="V14">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z14">
-        <v>3.14</v>
+        <v>4.03</v>
       </c>
       <c r="AA14">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AB14">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="AC14">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="AD14">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE14">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF14">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK14">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O15">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="P15">
-        <v>3.83</v>
+        <v>4.61</v>
       </c>
       <c r="Q15">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="R15">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T15">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="U15">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V15">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="W15">
         <v>1.08</v>
@@ -2799,16 +2799,16 @@
         <v>1.95</v>
       </c>
       <c r="AC15">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AD15">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE15">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AG15">
         <v>1.95</v>
@@ -2827,7 +2827,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="O16">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="P16">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q16">
         <v>3.06</v>
@@ -2932,13 +2932,13 @@
         <v>1.95</v>
       </c>
       <c r="S16">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="T16">
-        <v>2.27</v>
+        <v>2.54</v>
       </c>
       <c r="U16">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="V16">
         <v>1.29</v>
@@ -2953,13 +2953,13 @@
         <v>1.4</v>
       </c>
       <c r="Z16">
-        <v>2.62</v>
+        <v>2.91</v>
       </c>
       <c r="AA16">
         <v>2.25</v>
       </c>
       <c r="AB16">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC16">
         <v>4.5</v>
@@ -2990,7 +2990,7 @@
         <v>1.32</v>
       </c>
       <c r="AK16">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,25 +3080,25 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="O17">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="P17">
+        <v>2.9</v>
+      </c>
+      <c r="Q17">
         <v>3.07</v>
       </c>
-      <c r="Q17">
-        <v>3</v>
-      </c>
       <c r="R17">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S17">
         <v>1.5</v>
       </c>
       <c r="T17">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U17">
         <v>3.3</v>
@@ -3110,7 +3110,7 @@
         <v>1.05</v>
       </c>
       <c r="X17">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
         <v>1.42</v>
@@ -3119,25 +3119,25 @@
         <v>2.73</v>
       </c>
       <c r="AA17">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB17">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC17">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AD17">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF17">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG17">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK17">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3246,22 +3246,22 @@
         <v>1.25</v>
       </c>
       <c r="O18">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="P18">
         <v>11</v>
       </c>
       <c r="Q18">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R18">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="S18">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="U18">
         <v>2.27</v>
@@ -3270,7 +3270,7 @@
         <v>1.51</v>
       </c>
       <c r="W18">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X18">
         <v>1</v>
@@ -3285,7 +3285,7 @@
         <v>1.57</v>
       </c>
       <c r="AB18">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AC18">
         <v>2.45</v>
@@ -3297,10 +3297,10 @@
         <v>1.2</v>
       </c>
       <c r="AF18">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AG18">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK18">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3412,22 +3412,22 @@
         <v>3</v>
       </c>
       <c r="P19">
-        <v>3.6</v>
+        <v>3.23</v>
       </c>
       <c r="Q19">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="R19">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="S19">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T19">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U19">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="V19">
         <v>1.28</v>
@@ -3436,7 +3436,7 @@
         <v>1.02</v>
       </c>
       <c r="X19">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y19">
         <v>1.4</v>
@@ -3445,7 +3445,7 @@
         <v>2.88</v>
       </c>
       <c r="AA19">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AB19">
         <v>1.57</v>
@@ -3454,13 +3454,13 @@
         <v>4.33</v>
       </c>
       <c r="AD19">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE19">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AG19">
         <v>1.7</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
         <v>1.67</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="O20">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P20">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="Q20">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="R20">
         <v>2.06</v>
@@ -3587,19 +3587,19 @@
         <v>1.44</v>
       </c>
       <c r="T20">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U20">
         <v>3.18</v>
       </c>
       <c r="V20">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W20">
         <v>1.05</v>
       </c>
       <c r="X20">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
         <v>1.36</v>
@@ -3608,10 +3608,10 @@
         <v>2.7</v>
       </c>
       <c r="AA20">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AB20">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC20">
         <v>4.33</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
         <v>1.6</v>
@@ -3732,52 +3732,52 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="O21">
         <v>3.3</v>
       </c>
       <c r="P21">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q21">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="R21">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T21">
         <v>2.64</v>
       </c>
       <c r="U21">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="V21">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W21">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z21">
         <v>3.28</v>
       </c>
       <c r="AA21">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB21">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC21">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AD21">
         <v>1.28</v>
@@ -3786,10 +3786,10 @@
         <v>1.07</v>
       </c>
       <c r="AF21">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AG21">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -624,79 +624,79 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="O2">
-        <v>5.05</v>
+        <v>5.5</v>
       </c>
       <c r="P2">
-        <v>10.9</v>
+        <v>8.75</v>
       </c>
       <c r="Q2">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="R2">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="S2">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T2">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U2">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="V2">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z2">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA2">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB2">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC2">
         <v>2.15</v>
       </c>
       <c r="AD2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE2">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF2">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG2">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58", "67", "69", "76", "80", "89"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -705,37 +705,37 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AK2">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="O5">
         <v>2.91</v>
@@ -1133,13 +1133,13 @@
         <v>2.6</v>
       </c>
       <c r="Q5">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="R5">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S5">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T5">
         <v>2.51</v>
@@ -1154,7 +1154,7 @@
         <v>1.04</v>
       </c>
       <c r="X5">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y5">
         <v>1.33</v>
@@ -1172,16 +1172,16 @@
         <v>3.5</v>
       </c>
       <c r="AD5">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE5">
         <v>1.04</v>
       </c>
       <c r="AF5">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG5">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1264,26 +1264,26 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51", "64"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "62", "73"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1456,25 +1456,25 @@
         <v>3</v>
       </c>
       <c r="P7">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q7">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="R7">
         <v>2.06</v>
       </c>
       <c r="S7">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T7">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="U7">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="W7">
         <v>1.05</v>
@@ -1486,28 +1486,28 @@
         <v>1.4</v>
       </c>
       <c r="Z7">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="AA7">
         <v>2.24</v>
       </c>
       <c r="AB7">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC7">
-        <v>4.04</v>
+        <v>4.15</v>
       </c>
       <c r="AD7">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF7">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG7">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AK7">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O8">
+        <v>3.3</v>
+      </c>
+      <c r="P8">
         <v>3.1</v>
       </c>
-      <c r="P8">
-        <v>3.2</v>
-      </c>
       <c r="Q8">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="R8">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="S8">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="T8">
-        <v>2.51</v>
+        <v>2.76</v>
       </c>
       <c r="U8">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="V8">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z8">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="AA8">
         <v>2.15</v>
       </c>
       <c r="AB8">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AC8">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="AD8">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG8">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK8">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="O9">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="P9">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="Q9">
+        <v>2.75</v>
+      </c>
+      <c r="R9">
+        <v>2.02</v>
+      </c>
+      <c r="S9">
+        <v>1.35</v>
+      </c>
+      <c r="T9">
         <v>2.68</v>
       </c>
-      <c r="R9">
-        <v>1.96</v>
-      </c>
-      <c r="S9">
-        <v>1.38</v>
-      </c>
-      <c r="T9">
-        <v>2.65</v>
-      </c>
       <c r="U9">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="V9">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
         <v>1.05</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z9">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="AA9">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AB9">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC9">
         <v>3.5</v>
       </c>
       <c r="AD9">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE9">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG9">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK9">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,28 +1939,28 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="O10">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Q10">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="R10">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="S10">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T10">
         <v>3.6</v>
       </c>
       <c r="U10">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V10">
         <v>1.47</v>
@@ -1969,10 +1969,10 @@
         <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z10">
         <v>4.8</v>
@@ -1981,22 +1981,22 @@
         <v>1.57</v>
       </c>
       <c r="AB10">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC10">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="AD10">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE10">
         <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AG10">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.1</v>
       </c>
       <c r="AK10">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="O11">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="P11">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="Q11">
         <v>3.3</v>
@@ -2123,10 +2123,10 @@
         <v>2.75</v>
       </c>
       <c r="U11">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="V11">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W11">
         <v>1.04</v>
@@ -2159,7 +2159,7 @@
         <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2265,25 +2265,25 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="Q12">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="R12">
         <v>2.09</v>
       </c>
       <c r="S12">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="U12">
         <v>2.68</v>
@@ -2292,37 +2292,37 @@
         <v>1.37</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AA12">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AB12">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC12">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD12">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF12">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG12">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2600,7 +2600,7 @@
         <v>4.75</v>
       </c>
       <c r="Q14">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R14">
         <v>2.3</v>
@@ -2612,10 +2612,10 @@
         <v>3.1</v>
       </c>
       <c r="U14">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="V14">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W14">
         <v>1.06</v>
@@ -2627,13 +2627,13 @@
         <v>1.24</v>
       </c>
       <c r="Z14">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="AA14">
         <v>1.75</v>
       </c>
       <c r="AB14">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AC14">
         <v>2.88</v>
@@ -2642,13 +2642,13 @@
         <v>1.4</v>
       </c>
       <c r="AE14">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF14">
         <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK14">
         <v>2.4</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="O15">
-        <v>3.64</v>
+        <v>3.16</v>
       </c>
       <c r="P15">
-        <v>4.61</v>
+        <v>3.76</v>
       </c>
       <c r="Q15">
         <v>2.38</v>
       </c>
       <c r="R15">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S15">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T15">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U15">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="V15">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z15">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA15">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB15">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC15">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AD15">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE15">
         <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG15">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O16">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P16">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q16">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="R16">
         <v>1.95</v>
       </c>
       <c r="S16">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="T16">
         <v>2.54</v>
       </c>
       <c r="U16">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="V16">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W16">
         <v>1.03</v>
@@ -2965,7 +2965,7 @@
         <v>4.5</v>
       </c>
       <c r="AD16">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE16">
         <v>1.02</v>
@@ -2990,7 +2990,7 @@
         <v>1.32</v>
       </c>
       <c r="AK16">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O17">
+        <v>2.95</v>
+      </c>
+      <c r="P17">
         <v>3</v>
       </c>
-      <c r="P17">
-        <v>2.9</v>
-      </c>
       <c r="Q17">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="R17">
         <v>2</v>
@@ -3134,10 +3134,10 @@
         <v>1</v>
       </c>
       <c r="AF17">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG17">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="O18">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="P18">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q18">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R18">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="S18">
         <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U18">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V18">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W18">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z18">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA18">
         <v>1.57</v>
       </c>
       <c r="AB18">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="AC18">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AD18">
         <v>1.53</v>
       </c>
       <c r="AE18">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF18">
         <v>2.15</v>
       </c>
       <c r="AG18">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.03</v>
       </c>
       <c r="AK18">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,22 +3409,22 @@
         <v>2.05</v>
       </c>
       <c r="O19">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P19">
-        <v>3.23</v>
+        <v>3.47</v>
       </c>
       <c r="Q19">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="R19">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S19">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="T19">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="U19">
         <v>3</v>
@@ -3445,7 +3445,7 @@
         <v>2.88</v>
       </c>
       <c r="AA19">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AB19">
         <v>1.57</v>
@@ -3457,7 +3457,7 @@
         <v>1.16</v>
       </c>
       <c r="AE19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF19">
         <v>1.96</v>
@@ -3479,7 +3479,7 @@
         <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3575,13 +3575,13 @@
         <v>3.05</v>
       </c>
       <c r="P20">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="Q20">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="R20">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S20">
         <v>1.44</v>
@@ -3590,7 +3590,7 @@
         <v>2.36</v>
       </c>
       <c r="U20">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="V20">
         <v>1.29</v>
@@ -3605,7 +3605,7 @@
         <v>1.36</v>
       </c>
       <c r="Z20">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="AA20">
         <v>2.17</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK20">
         <v>1.6</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="O21">
         <v>3.3</v>
@@ -3741,55 +3741,55 @@
         <v>4.4</v>
       </c>
       <c r="Q21">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="R21">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="S21">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="U21">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V21">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W21">
         <v>1.08</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z21">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="AA21">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="AB21">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="AC21">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AD21">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AE21">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF21">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AG21">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,22 +4384,22 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="P25">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q25">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R25">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S25">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T25">
         <v>2.65</v>
@@ -4414,34 +4414,34 @@
         <v>1.04</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Z25">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AA25">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AB25">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AC25">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="AD25">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE25">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AG25">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4710,25 +4710,25 @@
         </is>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O27">
         <v>3</v>
       </c>
       <c r="P27">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q27">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="R27">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="S27">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T27">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U27">
         <v>3.18</v>
@@ -4737,25 +4737,25 @@
         <v>1.29</v>
       </c>
       <c r="W27">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y27">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z27">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="AA27">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AB27">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC27">
-        <v>4.4</v>
+        <v>4.37</v>
       </c>
       <c r="AD27">
         <v>1.22</v>
@@ -4764,10 +4764,10 @@
         <v>1.01</v>
       </c>
       <c r="AF27">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG27">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AK27">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL28">
         <v>0</v>

--- a/jogos_2026-09-21.xlsx
+++ b/jogos_2026-09-21.xlsx
@@ -775,13 +775,13 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -794,7 +794,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,7 +859,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1104,23 +1104,23 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "83"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1427,26 +1427,26 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40", "76", "90"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,26 +1590,26 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "28", "57", "69"]</t>
         </is>
       </c>
       <c r="AJ8">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1765,14 +1765,14 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -1855,16 +1855,16 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ9">
         <v>0</v>
@@ -1916,26 +1916,26 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "29", "57", "80"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "70"]</t>
         </is>
       </c>
       <c r="AJ10">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,26 +2079,26 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1", "77"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "58", "85"]</t>
         </is>
       </c>
       <c r="AJ11">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,16 +2242,16 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "31", "43", "45+1"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="O13">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="P13">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="Q13">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="R13">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="S13">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="T13">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="U13">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="V13">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W13">
         <v>1.03</v>
       </c>
       <c r="X13">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y13">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Z13">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA13">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AB13">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC13">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AD13">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>2.34</v>
+        <v>2.51</v>
       </c>
       <c r="AG13">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK13">
         <v>1.85</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2580,14 +2580,14 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47", "69"]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2734,13 +2734,13 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "19"]</t>
         </is>
       </c>
       <c r="AJ15">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3485,28 +3485,28 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3546,26 +3546,26 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "88"]</t>
         </is>
       </c>
       <c r="AJ20">
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,26 +3709,26 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1", "45", "54", "70"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
@@ -3811,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3891,35 +3891,35 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N22">
-        <v>2.33</v>
+        <v>2.92</v>
       </c>
       <c r="O22">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="P22">
-        <v>2.85</v>
+        <v>2.47</v>
       </c>
       <c r="Q22">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="R22">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S22">
         <v>1.42</v>
       </c>
       <c r="T22">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="U22">
-        <v>3.21</v>
+        <v>2.9</v>
       </c>
       <c r="V22">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W22">
         <v>1.05</v>
@@ -3928,31 +3928,31 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z22">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AA22">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="AB22">
         <v>1.5</v>
       </c>
       <c r="AC22">
-        <v>3.88</v>
+        <v>3.76</v>
       </c>
       <c r="AD22">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE22">
         <v>1.03</v>
       </c>
       <c r="AF22">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG22">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.34</v>
       </c>
       <c r="AK22">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,55 +4067,55 @@
         <v>3.1</v>
       </c>
       <c r="Q23">
-        <v>3.12</v>
+        <v>2.96</v>
       </c>
       <c r="R23">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="S23">
         <v>1.55</v>
       </c>
       <c r="T23">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="U23">
         <v>3.75</v>
       </c>
       <c r="V23">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W23">
         <v>1.04</v>
       </c>
       <c r="X23">
+        <v>1.1</v>
+      </c>
+      <c r="Y23">
+        <v>1.62</v>
+      </c>
+      <c r="Z23">
+        <v>2.32</v>
+      </c>
+      <c r="AA23">
+        <v>2.94</v>
+      </c>
+      <c r="AB23">
+        <v>1.36</v>
+      </c>
+      <c r="AC23">
+        <v>6.5</v>
+      </c>
+      <c r="AD23">
         <v>1.08</v>
       </c>
-      <c r="Y23">
-        <v>1.58</v>
-      </c>
-      <c r="Z23">
-        <v>2.39</v>
-      </c>
-      <c r="AA23">
-        <v>2.8</v>
-      </c>
-      <c r="AB23">
-        <v>1.42</v>
-      </c>
-      <c r="AC23">
-        <v>5.62</v>
-      </c>
-      <c r="AD23">
-        <v>1.1</v>
-      </c>
       <c r="AE23">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF23">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AG23">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4384,25 +4384,25 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="O25">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="P25">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="Q25">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="R25">
         <v>2</v>
       </c>
       <c r="S25">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="T25">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="U25">
         <v>3.1</v>
@@ -4417,13 +4417,13 @@
         <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z25">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AA25">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="AB25">
         <v>1.58</v>
@@ -4432,7 +4432,7 @@
         <v>4.1</v>
       </c>
       <c r="AD25">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE25">
         <v>1.06</v>
@@ -4441,7 +4441,7 @@
         <v>2.05</v>
       </c>
       <c r="AG25">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK25">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4543,11 +4543,11 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N26">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="O26">
         <v>3.2</v>
@@ -4562,13 +4562,13 @@
         <v>1.98</v>
       </c>
       <c r="S26">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T26">
+        <v>2.88</v>
+      </c>
+      <c r="U26">
         <v>2.77</v>
-      </c>
-      <c r="U26">
-        <v>2.75</v>
       </c>
       <c r="V26">
         <v>1.36</v>
@@ -4580,10 +4580,10 @@
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z26">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="AA26">
         <v>2</v>
@@ -4601,7 +4601,7 @@
         <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG26">
         <v>2</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AK26">
         <v>1.4</v>
@@ -4710,52 +4710,52 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O27">
         <v>3</v>
       </c>
       <c r="P27">
+        <v>3.4</v>
+      </c>
+      <c r="Q27">
+        <v>2.78</v>
+      </c>
+      <c r="R27">
+        <v>2.11</v>
+      </c>
+      <c r="S27">
+        <v>1.4</v>
+      </c>
+      <c r="T27">
+        <v>2.41</v>
+      </c>
+      <c r="U27">
         <v>3.3</v>
       </c>
-      <c r="Q27">
-        <v>2.76</v>
-      </c>
-      <c r="R27">
-        <v>1.98</v>
-      </c>
-      <c r="S27">
-        <v>1.48</v>
-      </c>
-      <c r="T27">
-        <v>2.5</v>
-      </c>
-      <c r="U27">
-        <v>3.18</v>
-      </c>
       <c r="V27">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y27">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z27">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="AA27">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="AB27">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC27">
-        <v>4.37</v>
+        <v>4.48</v>
       </c>
       <c r="AD27">
         <v>1.22</v>
@@ -4764,10 +4764,10 @@
         <v>1.01</v>
       </c>
       <c r="AF27">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AG27">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.31</v>
       </c>
       <c r="AK27">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AL27">
         <v>0</v>
